--- a/Notas_da_Copa_2026.xlsx
+++ b/Notas_da_Copa_2026.xlsx
@@ -3,23 +3,28 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="Resumo" sheetId="1" r:id="rId5"/>
-    <sheet state="visible" name="Quesitos" sheetId="2" r:id="rId6"/>
-    <sheet state="visible" name="Fase de grupos" sheetId="3" r:id="rId7"/>
-    <sheet state="visible" name="16 avos" sheetId="4" r:id="rId8"/>
-    <sheet state="visible" name="Oitavas de final" sheetId="5" r:id="rId9"/>
-    <sheet state="visible" name="Quartas de final" sheetId="6" r:id="rId10"/>
-    <sheet state="visible" name="Semifinais" sheetId="7" r:id="rId11"/>
-    <sheet state="visible" name="3º lugar" sheetId="8" r:id="rId12"/>
-    <sheet state="visible" name="Final" sheetId="9" r:id="rId13"/>
+    <sheet state="visible" name="Resumo" sheetId="1" r:id="rId4"/>
+    <sheet state="visible" name="Quesitos" sheetId="2" r:id="rId5"/>
+    <sheet state="visible" name="Fase de grupos" sheetId="3" r:id="rId6"/>
+    <sheet state="visible" name="16 avos" sheetId="4" r:id="rId7"/>
+    <sheet state="visible" name="Oitavas de final" sheetId="5" r:id="rId8"/>
+    <sheet state="visible" name="Quartas de final" sheetId="6" r:id="rId9"/>
+    <sheet state="visible" name="Semifinais" sheetId="7" r:id="rId10"/>
+    <sheet state="visible" name="3º lugar" sheetId="8" r:id="rId11"/>
+    <sheet state="visible" name="Final" sheetId="9" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr/>
+  <extLst>
+    <ext uri="GoogleSheetsCustomDataVersion2">
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId13" roundtripDataChecksum="8U1WRbd4SMpFGDb/uYUCbuTP/sCsBYV0eLHHPzK0UGk="/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="203">
   <si>
     <t>Controle de notas — Copa do Mundo 2026</t>
   </si>
@@ -243,7 +248,7 @@
     <t>17:00</t>
   </si>
   <si>
-    <t>Países Baixos x Japão</t>
+    <t>Holanda x Japão</t>
   </si>
   <si>
     <t>2-2</t>
@@ -309,12 +314,18 @@
     <t>Inglaterra x Croácia</t>
   </si>
   <si>
+    <t>4-2</t>
+  </si>
+  <si>
     <t>Gana x Panamá</t>
   </si>
   <si>
     <t>Uzbequistão x Colômbia</t>
   </si>
   <si>
+    <t>1-3</t>
+  </si>
+  <si>
     <t>Tchéquia x África do Sul</t>
   </si>
   <si>
@@ -345,7 +356,7 @@
     <t>Turquia x Paraguai</t>
   </si>
   <si>
-    <t>Países Baixos x Suécia</t>
+    <t>Holanda x Suécia</t>
   </si>
   <si>
     <t>Alemanha x Costa do Marfim</t>
@@ -390,9 +401,15 @@
     <t>Noruega x Senegal</t>
   </si>
   <si>
+    <t>3-2</t>
+  </si>
+  <si>
     <t>Jordânia x Argélia</t>
   </si>
   <si>
+    <t>1-2</t>
+  </si>
+  <si>
     <t>Portugal x Uzbequistão</t>
   </si>
   <si>
@@ -441,7 +458,7 @@
     <t>Japão x Suécia</t>
   </si>
   <si>
-    <t>Tunísia x Países Baixos</t>
+    <t>Tunísia x Holanda</t>
   </si>
   <si>
     <t>Turquia x Estados Unidos</t>
@@ -468,6 +485,9 @@
     <t>Nova Zelândia x Bélgica</t>
   </si>
   <si>
+    <t>1-5</t>
+  </si>
+  <si>
     <t>Panamá x Inglaterra</t>
   </si>
   <si>
@@ -486,6 +506,9 @@
     <t>Argélia x Áustria</t>
   </si>
   <si>
+    <t>3-3</t>
+  </si>
+  <si>
     <t>Jordânia x Argentina</t>
   </si>
   <si>
@@ -604,6 +627,9 @@
   </si>
   <si>
     <t>França x Inglaterra</t>
+  </si>
+  <si>
+    <t>4-6</t>
   </si>
   <si>
     <t>Espanha x Argentina</t>
@@ -613,9 +639,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <numFmts count="2">
+  <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
-    <numFmt numFmtId="165" formatCode="d-m"/>
   </numFmts>
   <fonts count="15">
     <font>
@@ -644,7 +669,6 @@
     <font>
       <color theme="1"/>
       <name val="Carlito"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11.0"/>
@@ -785,7 +809,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="45">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -800,9 +824,6 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="2" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment vertical="center"/>
@@ -857,6 +878,9 @@
     <xf borderId="0" fillId="10" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
+    <xf borderId="0" fillId="10" fontId="9" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
     <xf borderId="0" fillId="8" fontId="10" numFmtId="2" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
@@ -864,10 +888,7 @@
       <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="6" fontId="12" numFmtId="2" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="7" fontId="11" numFmtId="2" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="10" fontId="9" numFmtId="2" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
@@ -880,6 +901,9 @@
     </xf>
     <xf borderId="0" fillId="11" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="11" fontId="9" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="6" fontId="12" numFmtId="2" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" wrapText="1"/>
@@ -894,40 +918,28 @@
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="12" fontId="5" numFmtId="2" xfId="0" applyAlignment="1" applyFill="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="6" fontId="12" numFmtId="2" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="1"/>
+      <alignment horizontal="center"/>
     </xf>
     <xf borderId="0" fillId="5" fontId="13" numFmtId="2" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="1"/>
+      <alignment horizontal="center" shrinkToFit="0" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="9" fontId="14" numFmtId="2" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="10" fontId="9" numFmtId="2" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf borderId="0" fillId="11" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="11" fontId="9" numFmtId="2" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="11" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="11" fontId="9" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="10" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="10" fontId="9" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="10" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="11" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf borderId="0" fillId="10" fontId="9" numFmtId="2" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="10" fontId="9" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1111,10 +1123,6 @@
 
 <file path=xl/drawings/drawing9.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1457,7 +1465,6 @@
     <col customWidth="1" min="4" max="4" width="12.38"/>
     <col customWidth="1" min="5" max="5" width="6.75"/>
     <col customWidth="1" min="6" max="6" width="13.13"/>
-    <col customWidth="1" min="7" max="26" width="8.63"/>
   </cols>
   <sheetData>
     <row r="1" ht="30.0" customHeight="1">
@@ -1498,7 +1505,7 @@
       </c>
       <c r="F4" s="4">
         <f>IF(COUNT('Fase de grupos'!K3:K74)=0,"",ROUND(AVERAGE('Fase de grupos'!K3:K74),2))</f>
-        <v>6.25</v>
+        <v>6.26</v>
       </c>
     </row>
     <row r="5">
@@ -1507,10 +1514,10 @@
       </c>
       <c r="B5" s="3">
         <f>COUNT('Fase de grupos'!K3:K74,'16 avos'!K3:K18,'Oitavas de final'!K3:K10,'Quartas de final'!K3:K6,Semifinais!K3:K4,'3º lugar'!K3,Final!K3)</f>
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C5" s="3"/>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="3" t="s">
         <v>9</v>
       </c>
       <c r="E5" s="3">
@@ -1518,7 +1525,7 @@
       </c>
       <c r="F5" s="4">
         <f>IF(COUNT('16 avos'!K3:K18)=0,"",ROUND(AVERAGE('16 avos'!K3:K18),2))</f>
-        <v>7.25</v>
+        <v>7.28</v>
       </c>
     </row>
     <row r="6">
@@ -1527,7 +1534,7 @@
       </c>
       <c r="B6" s="4">
         <f>IF(B5=0,"",ROUND(SUM('Fase de grupos'!K3:K74,'16 avos'!K3:K18,'Oitavas de final'!K3:K10,'Quartas de final'!K3:K6,Semifinais!K3:K4,'3º lugar'!K3,Final!K3)/B5,2))</f>
-        <v>6.63</v>
+        <v>6.65</v>
       </c>
       <c r="C6" s="3"/>
       <c r="D6" s="3" t="s">
@@ -1547,7 +1554,7 @@
       </c>
       <c r="B7" s="4">
         <f>IF(B5=0,"",MAX('Fase de grupos'!K3:K74,'16 avos'!K3:K18,'Oitavas de final'!K3:K10,'Quartas de final'!K3:K6,Semifinais!K3:K4,'3º lugar'!K3,Final!K3))</f>
-        <v>9.5</v>
+        <v>9.63</v>
       </c>
       <c r="C7" s="3"/>
       <c r="D7" s="3" t="s">
@@ -1585,7 +1592,7 @@
       <c r="A9" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="6">
+      <c r="B9" s="5">
         <v>46190.0</v>
       </c>
       <c r="C9" s="3"/>
@@ -1610,9 +1617,9 @@
       <c r="E10" s="3">
         <v>1.0</v>
       </c>
-      <c r="F10" s="4" t="str">
+      <c r="F10" s="4">
         <f>IF(COUNT(Final!K3)=0,"",ROUND(AVERAGE(Final!K3),2))</f>
-        <v/>
+        <v>7.15</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>
@@ -2617,7 +2624,7 @@
     <col customWidth="1" min="2" max="2" width="10.0"/>
     <col customWidth="1" min="3" max="3" width="14.75"/>
     <col customWidth="1" min="4" max="4" width="26.63"/>
-    <col customWidth="1" min="5" max="26" width="8.63"/>
+    <col customWidth="1" min="5" max="6" width="8.63"/>
   </cols>
   <sheetData>
     <row r="1" ht="30.0" customHeight="1">
@@ -2640,86 +2647,86 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="B3" s="8">
+      <c r="B3" s="7">
         <v>2.5</v>
       </c>
-      <c r="C3" s="9">
+      <c r="C3" s="8">
         <v>0.25</v>
       </c>
-      <c r="D3" s="10" t="s">
+      <c r="D3" s="9" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="B4" s="8">
+      <c r="B4" s="7">
         <v>2.5</v>
       </c>
-      <c r="C4" s="9">
+      <c r="C4" s="8">
         <v>0.25</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="D4" s="9" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="s">
+      <c r="A5" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="B5" s="8">
+      <c r="B5" s="7">
         <v>2.0</v>
       </c>
-      <c r="C5" s="9">
+      <c r="C5" s="8">
         <v>0.2</v>
       </c>
-      <c r="D5" s="10" t="s">
+      <c r="D5" s="9" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B6" s="8">
+      <c r="B6" s="7">
         <v>2.0</v>
       </c>
-      <c r="C6" s="9">
+      <c r="C6" s="8">
         <v>0.2</v>
       </c>
-      <c r="D6" s="10" t="s">
+      <c r="D6" s="9" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="s">
+      <c r="A7" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B7" s="8">
+      <c r="B7" s="7">
         <v>1.0</v>
       </c>
-      <c r="C7" s="9">
+      <c r="C7" s="8">
         <v>0.1</v>
       </c>
-      <c r="D7" s="10" t="s">
+      <c r="D7" s="9" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="11" t="s">
+      <c r="A8" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="B8" s="12">
+      <c r="B8" s="11">
         <v>10.0</v>
       </c>
-      <c r="C8" s="13">
+      <c r="C8" s="12">
         <v>1.0</v>
       </c>
-      <c r="D8" s="14"/>
+      <c r="D8" s="13"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
@@ -2742,7 +2749,7 @@
       <c r="B12" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C12" s="15"/>
+      <c r="C12" s="14"/>
       <c r="D12" s="3" t="s">
         <v>41</v>
       </c>
@@ -2754,7 +2761,7 @@
       <c r="B13" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="C13" s="16"/>
+      <c r="C13" s="15"/>
       <c r="D13" s="3" t="s">
         <v>41</v>
       </c>
@@ -2766,7 +2773,7 @@
       <c r="B14" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="C14" s="17"/>
+      <c r="C14" s="16"/>
       <c r="D14" s="3" t="s">
         <v>41</v>
       </c>
@@ -2778,7 +2785,7 @@
       <c r="B15" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C15" s="18"/>
+      <c r="C15" s="17"/>
       <c r="D15" s="3" t="s">
         <v>41</v>
       </c>
@@ -2790,7 +2797,7 @@
       <c r="B16" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="C16" s="19"/>
+      <c r="C16" s="18"/>
       <c r="D16" s="3" t="s">
         <v>41</v>
       </c>
@@ -3800,63 +3807,62 @@
     <col customWidth="1" min="6" max="9" width="12.0"/>
     <col customWidth="1" min="10" max="10" width="20.0"/>
     <col customWidth="1" min="11" max="11" width="12.0"/>
-    <col customWidth="1" min="12" max="26" width="8.63"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.75" customHeight="1">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="19" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" ht="36.0" customHeight="1">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="21" t="s">
+      <c r="B2" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="C2" s="21" t="s">
+      <c r="C2" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="D2" s="21" t="s">
+      <c r="D2" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="E2" s="21" t="s">
+      <c r="E2" s="20" t="s">
         <v>50</v>
       </c>
-      <c r="F2" s="21" t="s">
+      <c r="F2" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="G2" s="21" t="s">
+      <c r="G2" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="H2" s="21" t="s">
+      <c r="H2" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="I2" s="21" t="s">
+      <c r="I2" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="J2" s="21" t="s">
+      <c r="J2" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="K2" s="21" t="s">
+      <c r="K2" s="20" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="22">
+      <c r="A3" s="21">
         <v>1.0</v>
       </c>
-      <c r="B3" s="23">
+      <c r="B3" s="22">
         <v>46184.0</v>
       </c>
-      <c r="C3" s="22" t="s">
+      <c r="C3" s="21" t="s">
         <v>52</v>
       </c>
-      <c r="D3" s="24" t="s">
+      <c r="D3" s="23" t="s">
         <v>53</v>
       </c>
-      <c r="E3" s="22" t="s">
+      <c r="E3" s="24" t="s">
         <v>54</v>
       </c>
       <c r="F3" s="25">
@@ -3868,31 +3874,31 @@
       <c r="H3" s="27">
         <v>4.0</v>
       </c>
-      <c r="I3" s="28">
+      <c r="I3" s="26">
         <v>6.0</v>
       </c>
       <c r="J3" s="25">
         <v>8.0</v>
       </c>
-      <c r="K3" s="29">
+      <c r="K3" s="28">
         <f>IF(COUNT(F3:J3)&lt;5,"",ROUND((F3*Quesitos!$B$3+G3*Quesitos!$B$4+H3*Quesitos!$B$5+I3*Quesitos!$B$6+J3*Quesitos!$B$7)/SUM(Quesitos!$B$3:$B$7),2))</f>
         <v>5.8</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="30">
+      <c r="A4" s="29">
         <v>2.0</v>
       </c>
-      <c r="B4" s="31">
+      <c r="B4" s="30">
         <v>46184.0</v>
       </c>
-      <c r="C4" s="30" t="s">
+      <c r="C4" s="29" t="s">
         <v>55</v>
       </c>
-      <c r="D4" s="32" t="s">
+      <c r="D4" s="31" t="s">
         <v>56</v>
       </c>
-      <c r="E4" s="30" t="s">
+      <c r="E4" s="32" t="s">
         <v>57</v>
       </c>
       <c r="F4" s="33">
@@ -3916,19 +3922,19 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="22">
+      <c r="A5" s="21">
         <v>3.0</v>
       </c>
-      <c r="B5" s="23">
+      <c r="B5" s="22">
         <v>46185.0</v>
       </c>
-      <c r="C5" s="22" t="s">
+      <c r="C5" s="21" t="s">
         <v>52</v>
       </c>
-      <c r="D5" s="24" t="s">
+      <c r="D5" s="23" t="s">
         <v>58</v>
       </c>
-      <c r="E5" s="22" t="s">
+      <c r="E5" s="24" t="s">
         <v>59</v>
       </c>
       <c r="F5" s="37">
@@ -3946,37 +3952,37 @@
       <c r="J5" s="37">
         <v>6.0</v>
       </c>
-      <c r="K5" s="29">
+      <c r="K5" s="28">
         <f>IF(COUNT(F5:J5)&lt;5,"",ROUND((F5*Quesitos!$B$3+G5*Quesitos!$B$4+H5*Quesitos!$B$5+I5*Quesitos!$B$6+J5*Quesitos!$B$7)/SUM(Quesitos!$B$3:$B$7),2))</f>
         <v>5.3</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="30">
+      <c r="A6" s="29">
         <v>4.0</v>
       </c>
-      <c r="B6" s="31">
+      <c r="B6" s="30">
         <v>46185.0</v>
       </c>
-      <c r="C6" s="30" t="s">
+      <c r="C6" s="29" t="s">
         <v>60</v>
       </c>
-      <c r="D6" s="32" t="s">
+      <c r="D6" s="31" t="s">
         <v>61</v>
       </c>
-      <c r="E6" s="30" t="s">
+      <c r="E6" s="32" t="s">
         <v>62</v>
       </c>
       <c r="F6" s="34">
         <v>8.0</v>
       </c>
-      <c r="G6" s="38">
+      <c r="G6" s="33">
         <v>5.0</v>
       </c>
-      <c r="H6" s="39">
+      <c r="H6" s="38">
         <v>4.0</v>
       </c>
-      <c r="I6" s="38">
+      <c r="I6" s="33">
         <v>5.0</v>
       </c>
       <c r="J6" s="34">
@@ -3988,19 +3994,19 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="22">
+      <c r="A7" s="21">
         <v>8.0</v>
       </c>
-      <c r="B7" s="23">
+      <c r="B7" s="22">
         <v>46186.0</v>
       </c>
-      <c r="C7" s="22" t="s">
+      <c r="C7" s="21" t="s">
         <v>52</v>
       </c>
-      <c r="D7" s="24" t="s">
+      <c r="D7" s="23" t="s">
         <v>63</v>
       </c>
-      <c r="E7" s="22" t="s">
+      <c r="E7" s="24" t="s">
         <v>59</v>
       </c>
       <c r="F7" s="33">
@@ -4012,37 +4018,37 @@
       <c r="H7" s="35">
         <v>5.0</v>
       </c>
-      <c r="I7" s="40">
+      <c r="I7" s="39">
         <v>9.0</v>
       </c>
       <c r="J7" s="35">
         <v>6.0</v>
       </c>
-      <c r="K7" s="29">
+      <c r="K7" s="28">
         <f>IF(COUNT(F7:J7)&lt;5,"",ROUND((F7*Quesitos!$B$3+G7*Quesitos!$B$4+H7*Quesitos!$B$5+I7*Quesitos!$B$6+J7*Quesitos!$B$7)/SUM(Quesitos!$B$3:$B$7),2))</f>
         <v>4.9</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="30">
+      <c r="A8" s="29">
         <v>7.0</v>
       </c>
-      <c r="B8" s="31">
+      <c r="B8" s="30">
         <v>46186.0</v>
       </c>
-      <c r="C8" s="30" t="s">
+      <c r="C8" s="29" t="s">
         <v>64</v>
       </c>
-      <c r="D8" s="32" t="s">
+      <c r="D8" s="31" t="s">
         <v>65</v>
       </c>
-      <c r="E8" s="30" t="s">
+      <c r="E8" s="32" t="s">
         <v>59</v>
       </c>
       <c r="F8" s="34">
         <v>7.0</v>
       </c>
-      <c r="G8" s="38">
+      <c r="G8" s="33">
         <v>4.0</v>
       </c>
       <c r="H8" s="34">
@@ -4060,70 +4066,70 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="22">
+      <c r="A9" s="21">
         <v>5.0</v>
       </c>
-      <c r="B9" s="23">
+      <c r="B9" s="22">
         <v>46186.0</v>
       </c>
-      <c r="C9" s="22" t="s">
+      <c r="C9" s="21" t="s">
         <v>60</v>
       </c>
-      <c r="D9" s="24" t="s">
+      <c r="D9" s="23" t="s">
         <v>66</v>
       </c>
-      <c r="E9" s="22" t="s">
+      <c r="E9" s="24" t="s">
         <v>67</v>
       </c>
-      <c r="F9" s="41">
+      <c r="F9" s="28">
         <v>5.0</v>
       </c>
-      <c r="G9" s="41">
+      <c r="G9" s="28">
         <v>6.0</v>
       </c>
-      <c r="H9" s="41">
+      <c r="H9" s="28">
         <v>6.0</v>
       </c>
-      <c r="I9" s="41">
+      <c r="I9" s="28">
         <v>7.0</v>
       </c>
-      <c r="J9" s="41">
+      <c r="J9" s="28">
         <v>5.5</v>
       </c>
-      <c r="K9" s="29">
+      <c r="K9" s="28">
         <f>IF(COUNT(F9:J9)&lt;5,"",ROUND((F9*Quesitos!$B$3+G9*Quesitos!$B$4+H9*Quesitos!$B$5+I9*Quesitos!$B$6+J9*Quesitos!$B$7)/SUM(Quesitos!$B$3:$B$7),2))</f>
         <v>5.9</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="30">
+      <c r="A10" s="29">
         <v>6.0</v>
       </c>
-      <c r="B10" s="31">
+      <c r="B10" s="30">
         <v>46187.0</v>
       </c>
-      <c r="C10" s="30" t="s">
+      <c r="C10" s="29" t="s">
         <v>68</v>
       </c>
-      <c r="D10" s="32" t="s">
+      <c r="D10" s="31" t="s">
         <v>69</v>
       </c>
-      <c r="E10" s="30" t="s">
+      <c r="E10" s="32" t="s">
         <v>54</v>
       </c>
-      <c r="F10" s="42">
+      <c r="F10" s="36">
         <v>6.0</v>
       </c>
-      <c r="G10" s="42">
+      <c r="G10" s="36">
         <v>6.0</v>
       </c>
-      <c r="H10" s="42">
+      <c r="H10" s="36">
         <v>6.0</v>
       </c>
-      <c r="I10" s="42">
+      <c r="I10" s="36">
         <v>7.0</v>
       </c>
-      <c r="J10" s="42">
+      <c r="J10" s="36">
         <v>4.0</v>
       </c>
       <c r="K10" s="36">
@@ -4132,70 +4138,70 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="22">
+      <c r="A11" s="21">
         <v>10.0</v>
       </c>
-      <c r="B11" s="23">
+      <c r="B11" s="22">
         <v>46187.0</v>
       </c>
-      <c r="C11" s="22" t="s">
+      <c r="C11" s="21" t="s">
         <v>70</v>
       </c>
-      <c r="D11" s="24" t="s">
+      <c r="D11" s="23" t="s">
         <v>71</v>
       </c>
-      <c r="E11" s="22" t="s">
+      <c r="E11" s="24" t="s">
         <v>72</v>
       </c>
-      <c r="F11" s="41">
+      <c r="F11" s="28">
         <v>8.0</v>
       </c>
-      <c r="G11" s="41">
+      <c r="G11" s="28">
         <v>7.0</v>
       </c>
-      <c r="H11" s="41">
+      <c r="H11" s="28">
         <v>4.0</v>
       </c>
-      <c r="I11" s="41">
+      <c r="I11" s="28">
         <v>3.0</v>
       </c>
-      <c r="J11" s="41">
+      <c r="J11" s="28">
         <v>7.0</v>
       </c>
-      <c r="K11" s="29">
+      <c r="K11" s="28">
         <f>IF(COUNT(F11:J11)&lt;5,"",ROUND((F11*Quesitos!$B$3+G11*Quesitos!$B$4+H11*Quesitos!$B$5+I11*Quesitos!$B$6+J11*Quesitos!$B$7)/SUM(Quesitos!$B$3:$B$7),2))</f>
         <v>5.85</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="30">
+      <c r="A12" s="29">
         <v>11.0</v>
       </c>
-      <c r="B12" s="31">
+      <c r="B12" s="30">
         <v>46187.0</v>
       </c>
-      <c r="C12" s="30" t="s">
+      <c r="C12" s="29" t="s">
         <v>73</v>
       </c>
-      <c r="D12" s="32" t="s">
+      <c r="D12" s="40" t="s">
         <v>74</v>
       </c>
-      <c r="E12" s="30" t="s">
+      <c r="E12" s="32" t="s">
         <v>75</v>
       </c>
-      <c r="F12" s="42">
+      <c r="F12" s="36">
         <v>7.0</v>
       </c>
-      <c r="G12" s="42">
+      <c r="G12" s="36">
         <v>7.0</v>
       </c>
-      <c r="H12" s="42">
+      <c r="H12" s="36">
         <v>9.0</v>
       </c>
-      <c r="I12" s="42">
+      <c r="I12" s="36">
         <v>8.0</v>
       </c>
-      <c r="J12" s="42">
+      <c r="J12" s="36">
         <v>5.0</v>
       </c>
       <c r="K12" s="36">
@@ -4204,70 +4210,70 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="22">
+      <c r="A13" s="21">
         <v>9.0</v>
       </c>
-      <c r="B13" s="23">
+      <c r="B13" s="22">
         <v>46187.0</v>
       </c>
-      <c r="C13" s="22" t="s">
+      <c r="C13" s="21" t="s">
         <v>76</v>
       </c>
-      <c r="D13" s="24" t="s">
+      <c r="D13" s="23" t="s">
         <v>77</v>
       </c>
-      <c r="E13" s="22" t="s">
+      <c r="E13" s="24" t="s">
         <v>78</v>
       </c>
-      <c r="F13" s="41">
+      <c r="F13" s="28">
         <v>8.0</v>
       </c>
-      <c r="G13" s="41">
+      <c r="G13" s="28">
         <v>8.0</v>
       </c>
-      <c r="H13" s="41">
+      <c r="H13" s="28">
         <v>10.0</v>
       </c>
-      <c r="I13" s="41">
+      <c r="I13" s="28">
         <v>8.0</v>
       </c>
-      <c r="J13" s="41">
+      <c r="J13" s="28">
         <v>2.0</v>
       </c>
-      <c r="K13" s="29">
+      <c r="K13" s="28">
         <f>IF(COUNT(F13:J13)&lt;5,"",ROUND((F13*Quesitos!$B$3+G13*Quesitos!$B$4+H13*Quesitos!$B$5+I13*Quesitos!$B$6+J13*Quesitos!$B$7)/SUM(Quesitos!$B$3:$B$7),2))</f>
         <v>7.8</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="30">
+      <c r="A14" s="29">
         <v>12.0</v>
       </c>
-      <c r="B14" s="31">
+      <c r="B14" s="30">
         <v>46187.0</v>
       </c>
-      <c r="C14" s="30" t="s">
+      <c r="C14" s="29" t="s">
         <v>55</v>
       </c>
-      <c r="D14" s="32" t="s">
+      <c r="D14" s="31" t="s">
         <v>79</v>
       </c>
-      <c r="E14" s="30" t="s">
+      <c r="E14" s="32" t="s">
         <v>80</v>
       </c>
-      <c r="F14" s="43">
+      <c r="F14" s="29">
         <v>7.5</v>
       </c>
-      <c r="G14" s="42">
+      <c r="G14" s="36">
         <v>7.0</v>
       </c>
-      <c r="H14" s="42">
+      <c r="H14" s="36">
         <v>5.0</v>
       </c>
-      <c r="I14" s="42">
+      <c r="I14" s="36">
         <v>5.0</v>
       </c>
-      <c r="J14" s="42">
+      <c r="J14" s="36">
         <v>2.0</v>
       </c>
       <c r="K14" s="36">
@@ -4276,70 +4282,70 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="22">
+      <c r="A15" s="21">
         <v>14.0</v>
       </c>
-      <c r="B15" s="23">
+      <c r="B15" s="22">
         <v>46188.0</v>
       </c>
-      <c r="C15" s="22" t="s">
+      <c r="C15" s="21" t="s">
         <v>81</v>
       </c>
-      <c r="D15" s="24" t="s">
+      <c r="D15" s="23" t="s">
         <v>82</v>
       </c>
-      <c r="E15" s="22" t="s">
+      <c r="E15" s="24" t="s">
         <v>83</v>
       </c>
-      <c r="F15" s="41">
+      <c r="F15" s="28">
         <v>3.0</v>
       </c>
-      <c r="G15" s="41">
+      <c r="G15" s="28">
         <v>7.0</v>
       </c>
-      <c r="H15" s="41">
+      <c r="H15" s="28">
         <v>4.0</v>
       </c>
-      <c r="I15" s="41">
+      <c r="I15" s="28">
         <v>10.0</v>
       </c>
-      <c r="J15" s="41">
+      <c r="J15" s="28">
         <v>10.0</v>
       </c>
-      <c r="K15" s="29">
+      <c r="K15" s="28">
         <f>IF(COUNT(F15:J15)&lt;5,"",ROUND((F15*Quesitos!$B$3+G15*Quesitos!$B$4+H15*Quesitos!$B$5+I15*Quesitos!$B$6+J15*Quesitos!$B$7)/SUM(Quesitos!$B$3:$B$7),2))</f>
         <v>6.3</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="30">
+      <c r="A16" s="29">
         <v>16.0</v>
       </c>
-      <c r="B16" s="31">
+      <c r="B16" s="30">
         <v>46188.0</v>
       </c>
-      <c r="C16" s="30" t="s">
+      <c r="C16" s="29" t="s">
         <v>52</v>
       </c>
-      <c r="D16" s="32" t="s">
+      <c r="D16" s="31" t="s">
         <v>84</v>
       </c>
-      <c r="E16" s="30" t="s">
+      <c r="E16" s="32" t="s">
         <v>59</v>
       </c>
-      <c r="F16" s="42">
+      <c r="F16" s="36">
         <v>5.0</v>
       </c>
-      <c r="G16" s="42">
+      <c r="G16" s="36">
         <v>5.0</v>
       </c>
-      <c r="H16" s="42">
+      <c r="H16" s="36">
         <v>6.0</v>
       </c>
-      <c r="I16" s="42">
+      <c r="I16" s="36">
         <v>6.0</v>
       </c>
-      <c r="J16" s="42">
+      <c r="J16" s="36">
         <v>4.0</v>
       </c>
       <c r="K16" s="36">
@@ -4348,70 +4354,70 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="22">
+      <c r="A17" s="21">
         <v>13.0</v>
       </c>
-      <c r="B17" s="23">
+      <c r="B17" s="22">
         <v>46188.0</v>
       </c>
-      <c r="C17" s="22" t="s">
+      <c r="C17" s="21" t="s">
         <v>64</v>
       </c>
-      <c r="D17" s="24" t="s">
+      <c r="D17" s="23" t="s">
         <v>85</v>
       </c>
-      <c r="E17" s="22" t="s">
+      <c r="E17" s="24" t="s">
         <v>59</v>
       </c>
-      <c r="F17" s="41">
+      <c r="F17" s="28">
         <v>4.0</v>
       </c>
-      <c r="G17" s="41">
+      <c r="G17" s="28">
         <v>4.0</v>
       </c>
-      <c r="H17" s="41">
+      <c r="H17" s="28">
         <v>7.0</v>
       </c>
-      <c r="I17" s="41">
+      <c r="I17" s="28">
         <v>7.0</v>
       </c>
-      <c r="J17" s="41">
+      <c r="J17" s="28">
         <v>4.0</v>
       </c>
-      <c r="K17" s="29">
+      <c r="K17" s="28">
         <f>IF(COUNT(F17:J17)&lt;5,"",ROUND((F17*Quesitos!$B$3+G17*Quesitos!$B$4+H17*Quesitos!$B$5+I17*Quesitos!$B$6+J17*Quesitos!$B$7)/SUM(Quesitos!$B$3:$B$7),2))</f>
         <v>5.2</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="30">
+      <c r="A18" s="29">
         <v>15.0</v>
       </c>
-      <c r="B18" s="31">
+      <c r="B18" s="30">
         <v>46188.0</v>
       </c>
-      <c r="C18" s="30" t="s">
+      <c r="C18" s="29" t="s">
         <v>60</v>
       </c>
-      <c r="D18" s="32" t="s">
+      <c r="D18" s="31" t="s">
         <v>86</v>
       </c>
-      <c r="E18" s="30" t="s">
+      <c r="E18" s="32" t="s">
         <v>75</v>
       </c>
-      <c r="F18" s="42">
+      <c r="F18" s="36">
         <v>7.0</v>
       </c>
-      <c r="G18" s="42">
+      <c r="G18" s="36">
         <v>7.0</v>
       </c>
-      <c r="H18" s="42">
+      <c r="H18" s="36">
         <v>8.0</v>
       </c>
-      <c r="I18" s="42">
+      <c r="I18" s="36">
         <v>9.0</v>
       </c>
-      <c r="J18" s="42">
+      <c r="J18" s="36">
         <v>4.0</v>
       </c>
       <c r="K18" s="36">
@@ -4420,70 +4426,70 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="22">
+      <c r="A19" s="21">
         <v>17.0</v>
       </c>
-      <c r="B19" s="23">
+      <c r="B19" s="22">
         <v>46189.0</v>
       </c>
-      <c r="C19" s="22" t="s">
+      <c r="C19" s="21" t="s">
         <v>52</v>
       </c>
-      <c r="D19" s="24" t="s">
+      <c r="D19" s="23" t="s">
         <v>87</v>
       </c>
-      <c r="E19" s="22" t="s">
+      <c r="E19" s="24" t="s">
         <v>88</v>
       </c>
-      <c r="F19" s="41">
+      <c r="F19" s="28">
         <v>7.0</v>
       </c>
-      <c r="G19" s="41">
+      <c r="G19" s="28">
         <v>9.0</v>
       </c>
-      <c r="H19" s="41">
+      <c r="H19" s="28">
         <v>8.0</v>
       </c>
-      <c r="I19" s="41">
+      <c r="I19" s="28">
         <v>7.0</v>
       </c>
-      <c r="J19" s="41">
+      <c r="J19" s="28">
         <v>5.0</v>
       </c>
-      <c r="K19" s="29">
+      <c r="K19" s="28">
         <f>IF(COUNT(F19:J19)&lt;5,"",ROUND((F19*Quesitos!$B$3+G19*Quesitos!$B$4+H19*Quesitos!$B$5+I19*Quesitos!$B$6+J19*Quesitos!$B$7)/SUM(Quesitos!$B$3:$B$7),2))</f>
         <v>7.5</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="30">
+      <c r="A20" s="29">
         <v>18.0</v>
       </c>
-      <c r="B20" s="31">
+      <c r="B20" s="30">
         <v>46189.0</v>
       </c>
-      <c r="C20" s="30" t="s">
+      <c r="C20" s="29" t="s">
         <v>64</v>
       </c>
-      <c r="D20" s="32" t="s">
+      <c r="D20" s="31" t="s">
         <v>89</v>
       </c>
-      <c r="E20" s="30" t="s">
+      <c r="E20" s="32" t="s">
         <v>90</v>
       </c>
-      <c r="F20" s="42">
+      <c r="F20" s="36">
         <v>5.0</v>
       </c>
-      <c r="G20" s="42">
+      <c r="G20" s="36">
         <v>7.0</v>
       </c>
-      <c r="H20" s="42">
+      <c r="H20" s="36">
         <v>5.0</v>
       </c>
-      <c r="I20" s="42">
+      <c r="I20" s="36">
         <v>5.0</v>
       </c>
-      <c r="J20" s="42">
+      <c r="J20" s="36">
         <v>9.0</v>
       </c>
       <c r="K20" s="36">
@@ -4492,70 +4498,70 @@
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="22">
+      <c r="A21" s="21">
         <v>19.0</v>
       </c>
-      <c r="B21" s="23">
+      <c r="B21" s="22">
         <v>46189.0</v>
       </c>
-      <c r="C21" s="22" t="s">
+      <c r="C21" s="21" t="s">
         <v>60</v>
       </c>
-      <c r="D21" s="24" t="s">
+      <c r="D21" s="23" t="s">
         <v>91</v>
       </c>
-      <c r="E21" s="22" t="s">
+      <c r="E21" s="24" t="s">
         <v>92</v>
       </c>
-      <c r="F21" s="41">
+      <c r="F21" s="28">
         <v>8.0</v>
       </c>
-      <c r="G21" s="41">
+      <c r="G21" s="28">
         <v>7.0</v>
       </c>
-      <c r="H21" s="41">
+      <c r="H21" s="28">
         <v>6.0</v>
       </c>
-      <c r="I21" s="41">
+      <c r="I21" s="28">
         <v>5.0</v>
       </c>
-      <c r="J21" s="41">
+      <c r="J21" s="28">
         <v>10.0</v>
       </c>
-      <c r="K21" s="29">
+      <c r="K21" s="28">
         <f>IF(COUNT(F21:J21)&lt;5,"",ROUND((F21*Quesitos!$B$3+G21*Quesitos!$B$4+H21*Quesitos!$B$5+I21*Quesitos!$B$6+J21*Quesitos!$B$7)/SUM(Quesitos!$B$3:$B$7),2))</f>
         <v>6.95</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="30">
+      <c r="A22" s="29">
         <v>20.0</v>
       </c>
-      <c r="B22" s="31">
+      <c r="B22" s="30">
         <v>46190.0</v>
       </c>
-      <c r="C22" s="30" t="s">
+      <c r="C22" s="29" t="s">
         <v>68</v>
       </c>
-      <c r="D22" s="32" t="s">
+      <c r="D22" s="31" t="s">
         <v>93</v>
       </c>
-      <c r="E22" s="30" t="s">
+      <c r="E22" s="32" t="s">
         <v>88</v>
       </c>
-      <c r="F22" s="42">
+      <c r="F22" s="36">
         <v>4.0</v>
       </c>
-      <c r="G22" s="42">
+      <c r="G22" s="36">
         <v>7.0</v>
       </c>
-      <c r="H22" s="42">
+      <c r="H22" s="36">
         <v>8.0</v>
       </c>
-      <c r="I22" s="42">
+      <c r="I22" s="36">
         <v>7.0</v>
       </c>
-      <c r="J22" s="42">
+      <c r="J22" s="36">
         <v>7.0</v>
       </c>
       <c r="K22" s="36">
@@ -4564,70 +4570,70 @@
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="22">
+      <c r="A23" s="21">
         <v>23.0</v>
       </c>
-      <c r="B23" s="23">
+      <c r="B23" s="22">
         <v>46190.0</v>
       </c>
-      <c r="C23" s="22" t="s">
+      <c r="C23" s="21" t="s">
         <v>70</v>
       </c>
-      <c r="D23" s="24" t="s">
+      <c r="D23" s="23" t="s">
         <v>94</v>
       </c>
-      <c r="E23" s="22" t="s">
+      <c r="E23" s="24" t="s">
         <v>59</v>
       </c>
-      <c r="F23" s="41">
+      <c r="F23" s="28">
         <v>5.0</v>
       </c>
-      <c r="G23" s="41">
+      <c r="G23" s="28">
         <v>3.0</v>
       </c>
-      <c r="H23" s="41">
+      <c r="H23" s="28">
         <v>4.0</v>
       </c>
-      <c r="I23" s="41">
+      <c r="I23" s="28">
         <v>8.0</v>
       </c>
-      <c r="J23" s="41">
+      <c r="J23" s="28">
         <v>8.0</v>
       </c>
-      <c r="K23" s="29">
+      <c r="K23" s="28">
         <f>IF(COUNT(F23:J23)&lt;5,"",ROUND((F23*Quesitos!$B$3+G23*Quesitos!$B$4+H23*Quesitos!$B$5+I23*Quesitos!$B$6+J23*Quesitos!$B$7)/SUM(Quesitos!$B$3:$B$7),2))</f>
         <v>5.2</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="30">
+      <c r="A24" s="29">
         <v>22.0</v>
       </c>
-      <c r="B24" s="31">
+      <c r="B24" s="30">
         <v>46190.0</v>
       </c>
-      <c r="C24" s="30" t="s">
+      <c r="C24" s="29" t="s">
         <v>73</v>
       </c>
-      <c r="D24" s="32" t="s">
+      <c r="D24" s="31" t="s">
         <v>95</v>
       </c>
-      <c r="E24" s="44">
-        <v>46057.0</v>
-      </c>
-      <c r="F24" s="42">
+      <c r="E24" s="32" t="s">
+        <v>96</v>
+      </c>
+      <c r="F24" s="36">
         <v>9.0</v>
       </c>
-      <c r="G24" s="42">
+      <c r="G24" s="36">
         <v>9.0</v>
       </c>
-      <c r="H24" s="42">
+      <c r="H24" s="36">
         <v>9.0</v>
       </c>
-      <c r="I24" s="42">
+      <c r="I24" s="36">
         <v>8.0</v>
       </c>
-      <c r="J24" s="42">
+      <c r="J24" s="36">
         <v>7.0</v>
       </c>
       <c r="K24" s="36">
@@ -4636,70 +4642,70 @@
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="22">
+      <c r="A25" s="21">
         <v>21.0</v>
       </c>
-      <c r="B25" s="23">
+      <c r="B25" s="22">
         <v>46190.0</v>
       </c>
-      <c r="C25" s="22" t="s">
+      <c r="C25" s="21" t="s">
         <v>76</v>
       </c>
-      <c r="D25" s="24" t="s">
-        <v>96</v>
-      </c>
-      <c r="E25" s="45" t="s">
+      <c r="D25" s="23" t="s">
+        <v>97</v>
+      </c>
+      <c r="E25" s="24" t="s">
         <v>83</v>
       </c>
-      <c r="F25" s="41">
+      <c r="F25" s="28">
         <v>2.0</v>
       </c>
-      <c r="G25" s="41">
+      <c r="G25" s="28">
         <v>7.0</v>
       </c>
-      <c r="H25" s="41">
+      <c r="H25" s="28">
         <v>7.0</v>
       </c>
-      <c r="I25" s="41">
+      <c r="I25" s="28">
         <v>10.0</v>
       </c>
-      <c r="J25" s="41">
+      <c r="J25" s="28">
         <v>3.0</v>
       </c>
-      <c r="K25" s="29">
+      <c r="K25" s="28">
         <f>IF(COUNT(F25:J25)&lt;5,"",ROUND((F25*Quesitos!$B$3+G25*Quesitos!$B$4+H25*Quesitos!$B$5+I25*Quesitos!$B$6+J25*Quesitos!$B$7)/SUM(Quesitos!$B$3:$B$7),2))</f>
         <v>5.95</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="30">
+      <c r="A26" s="29">
         <v>24.0</v>
       </c>
-      <c r="B26" s="31">
+      <c r="B26" s="30">
         <v>46190.0</v>
       </c>
-      <c r="C26" s="30" t="s">
+      <c r="C26" s="29" t="s">
         <v>55</v>
       </c>
-      <c r="D26" s="32" t="s">
-        <v>97</v>
-      </c>
-      <c r="E26" s="44">
-        <v>46082.0</v>
-      </c>
-      <c r="F26" s="42">
+      <c r="D26" s="31" t="s">
+        <v>98</v>
+      </c>
+      <c r="E26" s="32" t="s">
+        <v>99</v>
+      </c>
+      <c r="F26" s="36">
         <v>4.0</v>
       </c>
-      <c r="G26" s="42">
+      <c r="G26" s="36">
         <v>6.0</v>
       </c>
-      <c r="H26" s="42">
+      <c r="H26" s="36">
         <v>6.5</v>
       </c>
-      <c r="I26" s="42">
+      <c r="I26" s="36">
         <v>5.0</v>
       </c>
-      <c r="J26" s="42">
+      <c r="J26" s="36">
         <v>6.0</v>
       </c>
       <c r="K26" s="36">
@@ -4708,142 +4714,142 @@
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="22">
+      <c r="A27" s="21">
         <v>25.0</v>
       </c>
-      <c r="B27" s="23">
+      <c r="B27" s="22">
         <v>46191.0</v>
       </c>
-      <c r="C27" s="22" t="s">
+      <c r="C27" s="21" t="s">
         <v>81</v>
       </c>
-      <c r="D27" s="24" t="s">
-        <v>98</v>
-      </c>
-      <c r="E27" s="46">
-        <v>46023.0</v>
-      </c>
-      <c r="F27" s="41">
+      <c r="D27" s="23" t="s">
+        <v>100</v>
+      </c>
+      <c r="E27" s="24" t="s">
+        <v>59</v>
+      </c>
+      <c r="F27" s="28">
         <v>4.5</v>
       </c>
-      <c r="G27" s="41">
+      <c r="G27" s="28">
         <v>6.0</v>
       </c>
-      <c r="H27" s="41">
+      <c r="H27" s="28">
         <v>5.5</v>
       </c>
-      <c r="I27" s="41">
+      <c r="I27" s="28">
         <v>7.0</v>
       </c>
-      <c r="J27" s="41">
+      <c r="J27" s="28">
         <v>3.0</v>
       </c>
-      <c r="K27" s="29">
+      <c r="K27" s="28">
         <f>IF(COUNT(F27:J27)&lt;5,"",ROUND((F27*Quesitos!$B$3+G27*Quesitos!$B$4+H27*Quesitos!$B$5+I27*Quesitos!$B$6+J27*Quesitos!$B$7)/SUM(Quesitos!$B$3:$B$7),2))</f>
         <v>5.43</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="30">
+      <c r="A28" s="29">
         <v>26.0</v>
       </c>
-      <c r="B28" s="31">
+      <c r="B28" s="30">
         <v>46191.0</v>
       </c>
-      <c r="C28" s="30" t="s">
+      <c r="C28" s="29" t="s">
         <v>52</v>
       </c>
-      <c r="D28" s="32" t="s">
-        <v>99</v>
-      </c>
-      <c r="E28" s="44">
-        <v>46026.0</v>
-      </c>
-      <c r="F28" s="42">
+      <c r="D28" s="31" t="s">
+        <v>101</v>
+      </c>
+      <c r="E28" s="32" t="s">
+        <v>62</v>
+      </c>
+      <c r="F28" s="36">
         <v>3.0</v>
       </c>
-      <c r="G28" s="42">
-        <v>8.5</v>
-      </c>
-      <c r="H28" s="42">
-        <v>5.5</v>
-      </c>
-      <c r="I28" s="42">
+      <c r="G28" s="41">
+        <v>10.0</v>
+      </c>
+      <c r="H28" s="41">
+        <v>7.0</v>
+      </c>
+      <c r="I28" s="41">
+        <v>8.0</v>
+      </c>
+      <c r="J28" s="41">
         <v>5.0</v>
-      </c>
-      <c r="J28" s="42">
-        <v>4.0</v>
       </c>
       <c r="K28" s="36">
         <f>IF(COUNT(F28:J28)&lt;5,"",ROUND((F28*Quesitos!$B$3+G28*Quesitos!$B$4+H28*Quesitos!$B$5+I28*Quesitos!$B$6+J28*Quesitos!$B$7)/SUM(Quesitos!$B$3:$B$7),2))</f>
-        <v>5.38</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="22">
+      <c r="A29" s="21">
         <v>27.0</v>
       </c>
-      <c r="B29" s="23">
+      <c r="B29" s="22">
         <v>46191.0</v>
       </c>
-      <c r="C29" s="22" t="s">
+      <c r="C29" s="21" t="s">
         <v>64</v>
       </c>
-      <c r="D29" s="24" t="s">
-        <v>100</v>
-      </c>
-      <c r="E29" s="45" t="s">
-        <v>101</v>
-      </c>
-      <c r="F29" s="41">
+      <c r="D29" s="23" t="s">
+        <v>102</v>
+      </c>
+      <c r="E29" s="24" t="s">
+        <v>103</v>
+      </c>
+      <c r="F29" s="28">
         <v>8.0</v>
       </c>
-      <c r="G29" s="41">
+      <c r="G29" s="28">
         <v>9.0</v>
       </c>
-      <c r="H29" s="41">
+      <c r="H29" s="28">
         <v>1.0</v>
       </c>
-      <c r="I29" s="41">
+      <c r="I29" s="28">
         <v>4.0</v>
       </c>
-      <c r="J29" s="41">
+      <c r="J29" s="28">
         <v>5.0</v>
       </c>
-      <c r="K29" s="29">
+      <c r="K29" s="28">
         <f>IF(COUNT(F29:J29)&lt;5,"",ROUND((F29*Quesitos!$B$3+G29*Quesitos!$B$4+H29*Quesitos!$B$5+I29*Quesitos!$B$6+J29*Quesitos!$B$7)/SUM(Quesitos!$B$3:$B$7),2))</f>
         <v>5.75</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="30">
+      <c r="A30" s="29">
         <v>28.0</v>
       </c>
-      <c r="B30" s="31">
+      <c r="B30" s="30">
         <v>46191.0</v>
       </c>
-      <c r="C30" s="30" t="s">
+      <c r="C30" s="29" t="s">
         <v>60</v>
       </c>
-      <c r="D30" s="32" t="s">
-        <v>102</v>
-      </c>
-      <c r="E30" s="43" t="s">
+      <c r="D30" s="31" t="s">
+        <v>104</v>
+      </c>
+      <c r="E30" s="32" t="s">
         <v>78</v>
       </c>
-      <c r="F30" s="42">
+      <c r="F30" s="36">
         <v>5.0</v>
       </c>
-      <c r="G30" s="42">
+      <c r="G30" s="36">
         <v>5.0</v>
       </c>
-      <c r="H30" s="42">
+      <c r="H30" s="36">
         <v>8.0</v>
       </c>
-      <c r="I30" s="42">
+      <c r="I30" s="36">
         <v>4.0</v>
       </c>
-      <c r="J30" s="42">
+      <c r="J30" s="36">
         <v>5.0</v>
       </c>
       <c r="K30" s="36">
@@ -4852,70 +4858,70 @@
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="22">
+      <c r="A31" s="21">
         <v>32.0</v>
       </c>
-      <c r="B31" s="23">
+      <c r="B31" s="22">
         <v>46192.0</v>
       </c>
-      <c r="C31" s="22" t="s">
+      <c r="C31" s="21" t="s">
         <v>52</v>
       </c>
-      <c r="D31" s="24" t="s">
-        <v>103</v>
-      </c>
-      <c r="E31" s="45" t="s">
+      <c r="D31" s="23" t="s">
+        <v>105</v>
+      </c>
+      <c r="E31" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="F31" s="41">
+      <c r="F31" s="28">
         <v>7.0</v>
       </c>
-      <c r="G31" s="41">
+      <c r="G31" s="28">
         <v>4.0</v>
       </c>
-      <c r="H31" s="41">
+      <c r="H31" s="28">
         <v>6.0</v>
       </c>
-      <c r="I31" s="41">
+      <c r="I31" s="28">
         <v>5.0</v>
       </c>
-      <c r="J31" s="41">
+      <c r="J31" s="28">
         <v>5.0</v>
       </c>
-      <c r="K31" s="29">
+      <c r="K31" s="28">
         <f>IF(COUNT(F31:J31)&lt;5,"",ROUND((F31*Quesitos!$B$3+G31*Quesitos!$B$4+H31*Quesitos!$B$5+I31*Quesitos!$B$6+J31*Quesitos!$B$7)/SUM(Quesitos!$B$3:$B$7),2))</f>
         <v>5.45</v>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="30">
+      <c r="A32" s="29">
         <v>30.0</v>
       </c>
-      <c r="B32" s="31">
+      <c r="B32" s="30">
         <v>46192.0</v>
       </c>
-      <c r="C32" s="30" t="s">
+      <c r="C32" s="29" t="s">
         <v>64</v>
       </c>
-      <c r="D32" s="32" t="s">
-        <v>104</v>
-      </c>
-      <c r="E32" s="43" t="s">
+      <c r="D32" s="31" t="s">
+        <v>106</v>
+      </c>
+      <c r="E32" s="32" t="s">
         <v>67</v>
       </c>
-      <c r="F32" s="42">
+      <c r="F32" s="36">
         <v>7.0</v>
       </c>
-      <c r="G32" s="42">
+      <c r="G32" s="36">
         <v>4.5</v>
       </c>
-      <c r="H32" s="42">
+      <c r="H32" s="36">
         <v>6.0</v>
       </c>
-      <c r="I32" s="42">
+      <c r="I32" s="36">
         <v>5.0</v>
       </c>
-      <c r="J32" s="42">
+      <c r="J32" s="36">
         <v>4.5</v>
       </c>
       <c r="K32" s="36">
@@ -4924,70 +4930,70 @@
       </c>
     </row>
     <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="22">
+      <c r="A33" s="21">
         <v>29.0</v>
       </c>
-      <c r="B33" s="23">
+      <c r="B33" s="22">
         <v>46192.0</v>
       </c>
-      <c r="C33" s="22" t="s">
+      <c r="C33" s="21" t="s">
         <v>60</v>
       </c>
-      <c r="D33" s="24" t="s">
-        <v>105</v>
-      </c>
-      <c r="E33" s="45" t="s">
+      <c r="D33" s="23" t="s">
+        <v>107</v>
+      </c>
+      <c r="E33" s="24" t="s">
         <v>92</v>
       </c>
-      <c r="F33" s="41">
+      <c r="F33" s="28">
         <v>8.0</v>
       </c>
-      <c r="G33" s="41">
+      <c r="G33" s="28">
         <v>4.5</v>
       </c>
-      <c r="H33" s="41">
+      <c r="H33" s="28">
         <v>5.0</v>
       </c>
-      <c r="I33" s="41">
+      <c r="I33" s="28">
         <v>5.0</v>
       </c>
-      <c r="J33" s="41">
+      <c r="J33" s="28">
         <v>6.0</v>
       </c>
-      <c r="K33" s="29">
+      <c r="K33" s="28">
         <f>IF(COUNT(F33:J33)&lt;5,"",ROUND((F33*Quesitos!$B$3+G33*Quesitos!$B$4+H33*Quesitos!$B$5+I33*Quesitos!$B$6+J33*Quesitos!$B$7)/SUM(Quesitos!$B$3:$B$7),2))</f>
         <v>5.73</v>
       </c>
     </row>
     <row r="34" ht="15.75" customHeight="1">
-      <c r="A34" s="30">
+      <c r="A34" s="29">
         <v>31.0</v>
       </c>
-      <c r="B34" s="31">
+      <c r="B34" s="30">
         <v>46193.0</v>
       </c>
-      <c r="C34" s="30" t="s">
-        <v>106</v>
-      </c>
-      <c r="D34" s="32" t="s">
-        <v>107</v>
-      </c>
-      <c r="E34" s="43" t="s">
+      <c r="C34" s="29" t="s">
+        <v>108</v>
+      </c>
+      <c r="D34" s="31" t="s">
+        <v>109</v>
+      </c>
+      <c r="E34" s="32" t="s">
         <v>67</v>
       </c>
-      <c r="F34" s="42">
+      <c r="F34" s="36">
         <v>4.0</v>
       </c>
-      <c r="G34" s="42">
+      <c r="G34" s="36">
         <v>5.5</v>
       </c>
-      <c r="H34" s="42">
+      <c r="H34" s="36">
         <v>4.5</v>
       </c>
-      <c r="I34" s="42">
+      <c r="I34" s="36">
         <v>10.0</v>
       </c>
-      <c r="J34" s="42">
+      <c r="J34" s="36">
         <v>7.0</v>
       </c>
       <c r="K34" s="36">
@@ -4996,70 +5002,70 @@
       </c>
     </row>
     <row r="35" ht="15.75" customHeight="1">
-      <c r="A35" s="22">
+      <c r="A35" s="21">
         <v>35.0</v>
       </c>
-      <c r="B35" s="23">
+      <c r="B35" s="22">
         <v>46193.0</v>
       </c>
-      <c r="C35" s="22" t="s">
+      <c r="C35" s="21" t="s">
         <v>70</v>
       </c>
-      <c r="D35" s="24" t="s">
-        <v>108</v>
-      </c>
-      <c r="E35" s="46">
-        <v>46027.0</v>
-      </c>
-      <c r="F35" s="41">
+      <c r="D35" s="42" t="s">
+        <v>110</v>
+      </c>
+      <c r="E35" s="24" t="s">
+        <v>80</v>
+      </c>
+      <c r="F35" s="28">
         <v>9.0</v>
       </c>
-      <c r="G35" s="41">
+      <c r="G35" s="28">
         <v>7.5</v>
       </c>
-      <c r="H35" s="41">
+      <c r="H35" s="28">
         <v>10.0</v>
       </c>
-      <c r="I35" s="41">
+      <c r="I35" s="28">
         <v>5.0</v>
       </c>
-      <c r="J35" s="41">
+      <c r="J35" s="28">
         <v>5.0</v>
       </c>
-      <c r="K35" s="29">
+      <c r="K35" s="28">
         <f>IF(COUNT(F35:J35)&lt;5,"",ROUND((F35*Quesitos!$B$3+G35*Quesitos!$B$4+H35*Quesitos!$B$5+I35*Quesitos!$B$6+J35*Quesitos!$B$7)/SUM(Quesitos!$B$3:$B$7),2))</f>
         <v>7.63</v>
       </c>
     </row>
     <row r="36" ht="15.75" customHeight="1">
-      <c r="A36" s="30">
+      <c r="A36" s="29">
         <v>33.0</v>
       </c>
-      <c r="B36" s="31">
+      <c r="B36" s="30">
         <v>46193.0</v>
       </c>
-      <c r="C36" s="30" t="s">
+      <c r="C36" s="29" t="s">
         <v>73</v>
       </c>
-      <c r="D36" s="32" t="s">
-        <v>109</v>
-      </c>
-      <c r="E36" s="44">
-        <v>46024.0</v>
-      </c>
-      <c r="F36" s="42">
+      <c r="D36" s="31" t="s">
+        <v>111</v>
+      </c>
+      <c r="E36" s="32" t="s">
+        <v>57</v>
+      </c>
+      <c r="F36" s="36">
         <v>6.0</v>
       </c>
-      <c r="G36" s="42">
+      <c r="G36" s="36">
         <v>8.0</v>
       </c>
-      <c r="H36" s="42">
+      <c r="H36" s="36">
         <v>8.0</v>
       </c>
-      <c r="I36" s="42">
+      <c r="I36" s="36">
         <v>8.0</v>
       </c>
-      <c r="J36" s="42">
+      <c r="J36" s="36">
         <v>3.0</v>
       </c>
       <c r="K36" s="36">
@@ -5068,70 +5074,70 @@
       </c>
     </row>
     <row r="37" ht="15.75" customHeight="1">
-      <c r="A37" s="22">
+      <c r="A37" s="21">
         <v>34.0</v>
       </c>
-      <c r="B37" s="23">
+      <c r="B37" s="22">
         <v>46193.0</v>
       </c>
-      <c r="C37" s="22" t="s">
-        <v>110</v>
-      </c>
-      <c r="D37" s="24" t="s">
-        <v>111</v>
-      </c>
-      <c r="E37" s="45" t="s">
+      <c r="C37" s="21" t="s">
+        <v>112</v>
+      </c>
+      <c r="D37" s="23" t="s">
+        <v>113</v>
+      </c>
+      <c r="E37" s="24" t="s">
         <v>83</v>
       </c>
-      <c r="F37" s="41">
+      <c r="F37" s="28">
         <v>6.0</v>
       </c>
-      <c r="G37" s="41">
+      <c r="G37" s="28">
         <v>3.0</v>
       </c>
-      <c r="H37" s="41">
+      <c r="H37" s="28">
         <v>6.0</v>
       </c>
-      <c r="I37" s="41">
+      <c r="I37" s="28">
         <v>8.0</v>
       </c>
-      <c r="J37" s="41">
+      <c r="J37" s="28">
         <v>10.0</v>
       </c>
-      <c r="K37" s="29">
+      <c r="K37" s="28">
         <f>IF(COUNT(F37:J37)&lt;5,"",ROUND((F37*Quesitos!$B$3+G37*Quesitos!$B$4+H37*Quesitos!$B$5+I37*Quesitos!$B$6+J37*Quesitos!$B$7)/SUM(Quesitos!$B$3:$B$7),2))</f>
         <v>6.05</v>
       </c>
     </row>
     <row r="38" ht="15.75" customHeight="1">
-      <c r="A38" s="30">
+      <c r="A38" s="29">
         <v>36.0</v>
       </c>
-      <c r="B38" s="31">
+      <c r="B38" s="30">
         <v>46194.0</v>
       </c>
-      <c r="C38" s="30" t="s">
+      <c r="C38" s="29" t="s">
         <v>68</v>
       </c>
-      <c r="D38" s="32" t="s">
-        <v>112</v>
-      </c>
-      <c r="E38" s="43" t="s">
-        <v>113</v>
-      </c>
-      <c r="F38" s="42">
+      <c r="D38" s="31" t="s">
+        <v>114</v>
+      </c>
+      <c r="E38" s="32" t="s">
+        <v>115</v>
+      </c>
+      <c r="F38" s="36">
         <v>7.0</v>
       </c>
-      <c r="G38" s="42">
+      <c r="G38" s="36">
         <v>6.0</v>
       </c>
-      <c r="H38" s="42">
+      <c r="H38" s="36">
         <v>4.0</v>
       </c>
-      <c r="I38" s="42">
+      <c r="I38" s="36">
         <v>6.0</v>
       </c>
-      <c r="J38" s="42">
+      <c r="J38" s="36">
         <v>9.0</v>
       </c>
       <c r="K38" s="36">
@@ -5140,70 +5146,70 @@
       </c>
     </row>
     <row r="39" ht="15.75" customHeight="1">
-      <c r="A39" s="22">
+      <c r="A39" s="21">
         <v>38.0</v>
       </c>
-      <c r="B39" s="23">
+      <c r="B39" s="22">
         <v>46194.0</v>
       </c>
-      <c r="C39" s="22" t="s">
+      <c r="C39" s="21" t="s">
         <v>81</v>
       </c>
-      <c r="D39" s="24" t="s">
-        <v>114</v>
-      </c>
-      <c r="E39" s="45" t="s">
-        <v>115</v>
-      </c>
-      <c r="F39" s="41">
+      <c r="D39" s="23" t="s">
+        <v>116</v>
+      </c>
+      <c r="E39" s="24" t="s">
+        <v>117</v>
+      </c>
+      <c r="F39" s="28">
         <v>8.5</v>
       </c>
-      <c r="G39" s="41">
+      <c r="G39" s="28">
         <v>3.0</v>
       </c>
-      <c r="H39" s="41">
+      <c r="H39" s="28">
         <v>3.0</v>
       </c>
-      <c r="I39" s="41">
+      <c r="I39" s="28">
         <v>7.0</v>
       </c>
-      <c r="J39" s="41">
+      <c r="J39" s="28">
         <v>6.0</v>
       </c>
-      <c r="K39" s="29">
+      <c r="K39" s="28">
         <f>IF(COUNT(F39:J39)&lt;5,"",ROUND((F39*Quesitos!$B$3+G39*Quesitos!$B$4+H39*Quesitos!$B$5+I39*Quesitos!$B$6+J39*Quesitos!$B$7)/SUM(Quesitos!$B$3:$B$7),2))</f>
         <v>5.48</v>
       </c>
     </row>
     <row r="40" ht="15.75" customHeight="1">
-      <c r="A40" s="30">
+      <c r="A40" s="29">
         <v>39.0</v>
       </c>
-      <c r="B40" s="31">
+      <c r="B40" s="30">
         <v>46194.0</v>
       </c>
-      <c r="C40" s="30" t="s">
+      <c r="C40" s="29" t="s">
         <v>52</v>
       </c>
-      <c r="D40" s="32" t="s">
-        <v>116</v>
-      </c>
-      <c r="E40" s="43" t="s">
+      <c r="D40" s="31" t="s">
+        <v>118</v>
+      </c>
+      <c r="E40" s="32" t="s">
         <v>83</v>
       </c>
-      <c r="F40" s="42">
+      <c r="F40" s="36">
         <v>5.0</v>
       </c>
-      <c r="G40" s="42">
+      <c r="G40" s="36">
         <v>5.0</v>
       </c>
-      <c r="H40" s="42">
+      <c r="H40" s="36">
         <v>7.0</v>
       </c>
-      <c r="I40" s="42">
+      <c r="I40" s="36">
         <v>7.5</v>
       </c>
-      <c r="J40" s="42">
+      <c r="J40" s="36">
         <v>2.0</v>
       </c>
       <c r="K40" s="36">
@@ -5212,70 +5218,70 @@
       </c>
     </row>
     <row r="41" ht="15.75" customHeight="1">
-      <c r="A41" s="22">
+      <c r="A41" s="21">
         <v>37.0</v>
       </c>
-      <c r="B41" s="23">
+      <c r="B41" s="22">
         <v>46194.0</v>
       </c>
-      <c r="C41" s="22" t="s">
+      <c r="C41" s="21" t="s">
         <v>64</v>
       </c>
-      <c r="D41" s="24" t="s">
-        <v>117</v>
-      </c>
-      <c r="E41" s="46">
-        <v>46055.0</v>
-      </c>
-      <c r="F41" s="41">
+      <c r="D41" s="23" t="s">
+        <v>119</v>
+      </c>
+      <c r="E41" s="24" t="s">
+        <v>75</v>
+      </c>
+      <c r="F41" s="28">
         <v>8.0</v>
       </c>
-      <c r="G41" s="41">
+      <c r="G41" s="28">
         <v>8.5</v>
       </c>
-      <c r="H41" s="41">
+      <c r="H41" s="28">
         <v>8.0</v>
       </c>
-      <c r="I41" s="41">
+      <c r="I41" s="28">
         <v>10.0</v>
       </c>
-      <c r="J41" s="41">
+      <c r="J41" s="28">
         <v>7.0</v>
       </c>
-      <c r="K41" s="29">
+      <c r="K41" s="28">
         <f>IF(COUNT(F41:J41)&lt;5,"",ROUND((F41*Quesitos!$B$3+G41*Quesitos!$B$4+H41*Quesitos!$B$5+I41*Quesitos!$B$6+J41*Quesitos!$B$7)/SUM(Quesitos!$B$3:$B$7),2))</f>
         <v>8.43</v>
       </c>
     </row>
     <row r="42" ht="15.75" customHeight="1">
-      <c r="A42" s="30">
+      <c r="A42" s="29">
         <v>40.0</v>
       </c>
-      <c r="B42" s="31">
+      <c r="B42" s="30">
         <v>46194.0</v>
       </c>
-      <c r="C42" s="30" t="s">
+      <c r="C42" s="29" t="s">
         <v>60</v>
       </c>
-      <c r="D42" s="32" t="s">
-        <v>118</v>
-      </c>
-      <c r="E42" s="44">
-        <v>46082.0</v>
-      </c>
-      <c r="F42" s="42">
+      <c r="D42" s="31" t="s">
+        <v>120</v>
+      </c>
+      <c r="E42" s="32" t="s">
+        <v>99</v>
+      </c>
+      <c r="F42" s="36">
         <v>7.0</v>
       </c>
-      <c r="G42" s="42">
+      <c r="G42" s="36">
         <v>7.5</v>
       </c>
-      <c r="H42" s="42">
+      <c r="H42" s="36">
         <v>7.0</v>
       </c>
-      <c r="I42" s="42">
+      <c r="I42" s="36">
         <v>6.0</v>
       </c>
-      <c r="J42" s="42">
+      <c r="J42" s="36">
         <v>9.0</v>
       </c>
       <c r="K42" s="36">
@@ -5284,70 +5290,70 @@
       </c>
     </row>
     <row r="43" ht="15.75" customHeight="1">
-      <c r="A43" s="22">
+      <c r="A43" s="21">
         <v>43.0</v>
       </c>
-      <c r="B43" s="23">
+      <c r="B43" s="22">
         <v>46195.0</v>
       </c>
-      <c r="C43" s="22" t="s">
+      <c r="C43" s="21" t="s">
         <v>70</v>
       </c>
-      <c r="D43" s="24" t="s">
-        <v>119</v>
-      </c>
-      <c r="E43" s="45" t="s">
+      <c r="D43" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="E43" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="F43" s="41">
+      <c r="F43" s="28">
         <v>7.0</v>
       </c>
-      <c r="G43" s="41">
+      <c r="G43" s="28">
         <v>6.5</v>
       </c>
-      <c r="H43" s="41">
+      <c r="H43" s="28">
         <v>7.0</v>
       </c>
-      <c r="I43" s="41">
+      <c r="I43" s="28">
         <v>5.0</v>
       </c>
-      <c r="J43" s="41">
+      <c r="J43" s="28">
         <v>8.0</v>
       </c>
-      <c r="K43" s="29">
+      <c r="K43" s="28">
         <f>IF(COUNT(F43:J43)&lt;5,"",ROUND((F43*Quesitos!$B$3+G43*Quesitos!$B$4+H43*Quesitos!$B$5+I43*Quesitos!$B$6+J43*Quesitos!$B$7)/SUM(Quesitos!$B$3:$B$7),2))</f>
         <v>6.58</v>
       </c>
     </row>
     <row r="44" ht="15.75" customHeight="1">
-      <c r="A44" s="30">
+      <c r="A44" s="29">
         <v>42.0</v>
       </c>
-      <c r="B44" s="31">
+      <c r="B44" s="30">
         <v>46195.0</v>
       </c>
-      <c r="C44" s="30" t="s">
-        <v>120</v>
-      </c>
-      <c r="D44" s="32" t="s">
-        <v>121</v>
-      </c>
-      <c r="E44" s="43" t="s">
+      <c r="C44" s="29" t="s">
+        <v>122</v>
+      </c>
+      <c r="D44" s="31" t="s">
+        <v>123</v>
+      </c>
+      <c r="E44" s="32" t="s">
         <v>92</v>
       </c>
-      <c r="F44" s="42">
+      <c r="F44" s="36">
         <v>6.5</v>
       </c>
-      <c r="G44" s="42">
+      <c r="G44" s="36">
         <v>7.0</v>
       </c>
-      <c r="H44" s="42">
+      <c r="H44" s="36">
         <v>4.0</v>
       </c>
-      <c r="I44" s="42">
+      <c r="I44" s="36">
         <v>3.0</v>
       </c>
-      <c r="J44" s="42">
+      <c r="J44" s="36">
         <v>5.0</v>
       </c>
       <c r="K44" s="36">
@@ -5356,70 +5362,70 @@
       </c>
     </row>
     <row r="45" ht="15.75" customHeight="1">
-      <c r="A45" s="22">
+      <c r="A45" s="21">
         <v>41.0</v>
       </c>
-      <c r="B45" s="23">
+      <c r="B45" s="22">
         <v>46195.0</v>
       </c>
-      <c r="C45" s="22" t="s">
-        <v>110</v>
-      </c>
-      <c r="D45" s="24" t="s">
-        <v>122</v>
-      </c>
-      <c r="E45" s="46">
-        <v>46056.0</v>
-      </c>
-      <c r="F45" s="41">
+      <c r="C45" s="21" t="s">
+        <v>112</v>
+      </c>
+      <c r="D45" s="23" t="s">
+        <v>124</v>
+      </c>
+      <c r="E45" s="24" t="s">
+        <v>125</v>
+      </c>
+      <c r="F45" s="28">
         <v>7.0</v>
       </c>
-      <c r="G45" s="41">
+      <c r="G45" s="28">
         <v>7.5</v>
       </c>
-      <c r="H45" s="41">
+      <c r="H45" s="28">
         <v>8.0</v>
       </c>
-      <c r="I45" s="41">
+      <c r="I45" s="28">
         <v>7.5</v>
       </c>
-      <c r="J45" s="41">
+      <c r="J45" s="28">
         <v>5.0</v>
       </c>
-      <c r="K45" s="29">
+      <c r="K45" s="28">
         <f>IF(COUNT(F45:J45)&lt;5,"",ROUND((F45*Quesitos!$B$3+G45*Quesitos!$B$4+H45*Quesitos!$B$5+I45*Quesitos!$B$6+J45*Quesitos!$B$7)/SUM(Quesitos!$B$3:$B$7),2))</f>
         <v>7.23</v>
       </c>
     </row>
     <row r="46" ht="15.75" customHeight="1">
-      <c r="A46" s="30">
+      <c r="A46" s="29">
         <v>44.0</v>
       </c>
-      <c r="B46" s="31">
+      <c r="B46" s="30">
         <v>46196.0</v>
       </c>
-      <c r="C46" s="30" t="s">
-        <v>106</v>
-      </c>
-      <c r="D46" s="32" t="s">
-        <v>123</v>
-      </c>
-      <c r="E46" s="44">
-        <v>46054.0</v>
-      </c>
-      <c r="F46" s="42">
+      <c r="C46" s="29" t="s">
+        <v>108</v>
+      </c>
+      <c r="D46" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="E46" s="32" t="s">
+        <v>127</v>
+      </c>
+      <c r="F46" s="36">
         <v>3.0</v>
       </c>
-      <c r="G46" s="42">
+      <c r="G46" s="36">
         <v>4.0</v>
       </c>
-      <c r="H46" s="42">
+      <c r="H46" s="36">
         <v>7.5</v>
       </c>
-      <c r="I46" s="42">
+      <c r="I46" s="36">
         <v>7.0</v>
       </c>
-      <c r="J46" s="42">
+      <c r="J46" s="36">
         <v>6.0</v>
       </c>
       <c r="K46" s="36">
@@ -5428,70 +5434,70 @@
       </c>
     </row>
     <row r="47" ht="15.75" customHeight="1">
-      <c r="A47" s="22">
+      <c r="A47" s="21">
         <v>47.0</v>
       </c>
-      <c r="B47" s="23">
+      <c r="B47" s="22">
         <v>46196.0</v>
       </c>
-      <c r="C47" s="22" t="s">
+      <c r="C47" s="21" t="s">
         <v>70</v>
       </c>
-      <c r="D47" s="24" t="s">
-        <v>124</v>
-      </c>
-      <c r="E47" s="45" t="s">
-        <v>125</v>
-      </c>
-      <c r="F47" s="41">
+      <c r="D47" s="23" t="s">
+        <v>128</v>
+      </c>
+      <c r="E47" s="24" t="s">
+        <v>129</v>
+      </c>
+      <c r="F47" s="28">
         <v>8.0</v>
       </c>
-      <c r="G47" s="41">
+      <c r="G47" s="28">
         <v>5.0</v>
       </c>
-      <c r="H47" s="41">
+      <c r="H47" s="28">
         <v>4.0</v>
       </c>
-      <c r="I47" s="41">
+      <c r="I47" s="28">
         <v>5.0</v>
       </c>
-      <c r="J47" s="41">
+      <c r="J47" s="28">
         <v>8.0</v>
       </c>
-      <c r="K47" s="29">
+      <c r="K47" s="28">
         <f>IF(COUNT(F47:J47)&lt;5,"",ROUND((F47*Quesitos!$B$3+G47*Quesitos!$B$4+H47*Quesitos!$B$5+I47*Quesitos!$B$6+J47*Quesitos!$B$7)/SUM(Quesitos!$B$3:$B$7),2))</f>
         <v>5.85</v>
       </c>
     </row>
     <row r="48" ht="15.75" customHeight="1">
-      <c r="A48" s="30">
+      <c r="A48" s="29">
         <v>45.0</v>
       </c>
-      <c r="B48" s="31">
+      <c r="B48" s="30">
         <v>46196.0</v>
       </c>
-      <c r="C48" s="30" t="s">
+      <c r="C48" s="29" t="s">
         <v>73</v>
       </c>
-      <c r="D48" s="32" t="s">
-        <v>126</v>
-      </c>
-      <c r="E48" s="43" t="s">
+      <c r="D48" s="31" t="s">
+        <v>130</v>
+      </c>
+      <c r="E48" s="32" t="s">
         <v>83</v>
       </c>
-      <c r="F48" s="42">
+      <c r="F48" s="36">
         <v>6.0</v>
       </c>
-      <c r="G48" s="42">
+      <c r="G48" s="36">
         <v>7.5</v>
       </c>
-      <c r="H48" s="42">
+      <c r="H48" s="36">
         <v>7.0</v>
       </c>
-      <c r="I48" s="42">
+      <c r="I48" s="36">
         <v>8.0</v>
       </c>
-      <c r="J48" s="42">
+      <c r="J48" s="36">
         <v>5.0</v>
       </c>
       <c r="K48" s="36">
@@ -5500,70 +5506,70 @@
       </c>
     </row>
     <row r="49" ht="15.75" customHeight="1">
-      <c r="A49" s="22">
+      <c r="A49" s="21">
         <v>46.0</v>
       </c>
-      <c r="B49" s="23">
+      <c r="B49" s="22">
         <v>46196.0</v>
       </c>
-      <c r="C49" s="22" t="s">
+      <c r="C49" s="21" t="s">
         <v>76</v>
       </c>
-      <c r="D49" s="24" t="s">
-        <v>127</v>
-      </c>
-      <c r="E49" s="45" t="s">
+      <c r="D49" s="23" t="s">
+        <v>131</v>
+      </c>
+      <c r="E49" s="24" t="s">
         <v>67</v>
       </c>
-      <c r="F49" s="41">
+      <c r="F49" s="28">
         <v>4.0</v>
       </c>
-      <c r="G49" s="41">
+      <c r="G49" s="28">
         <v>5.5</v>
       </c>
-      <c r="H49" s="41">
+      <c r="H49" s="28">
         <v>7.5</v>
       </c>
-      <c r="I49" s="41">
+      <c r="I49" s="28">
         <v>7.0</v>
       </c>
-      <c r="J49" s="41">
+      <c r="J49" s="28">
         <v>5.0</v>
       </c>
-      <c r="K49" s="29">
+      <c r="K49" s="28">
         <f>IF(COUNT(F49:J49)&lt;5,"",ROUND((F49*Quesitos!$B$3+G49*Quesitos!$B$4+H49*Quesitos!$B$5+I49*Quesitos!$B$6+J49*Quesitos!$B$7)/SUM(Quesitos!$B$3:$B$7),2))</f>
         <v>5.78</v>
       </c>
     </row>
     <row r="50" ht="15.75" customHeight="1">
-      <c r="A50" s="30">
+      <c r="A50" s="29">
         <v>48.0</v>
       </c>
-      <c r="B50" s="31">
+      <c r="B50" s="30">
         <v>46196.0</v>
       </c>
-      <c r="C50" s="30" t="s">
+      <c r="C50" s="29" t="s">
         <v>55</v>
       </c>
-      <c r="D50" s="32" t="s">
-        <v>128</v>
-      </c>
-      <c r="E50" s="43" t="s">
+      <c r="D50" s="31" t="s">
+        <v>132</v>
+      </c>
+      <c r="E50" s="32" t="s">
         <v>78</v>
       </c>
-      <c r="F50" s="42">
+      <c r="F50" s="36">
         <v>6.0</v>
       </c>
-      <c r="G50" s="42">
+      <c r="G50" s="36">
         <v>7.0</v>
       </c>
-      <c r="H50" s="42">
+      <c r="H50" s="36">
         <v>7.0</v>
       </c>
-      <c r="I50" s="42">
+      <c r="I50" s="36">
         <v>7.0</v>
       </c>
-      <c r="J50" s="42">
+      <c r="J50" s="36">
         <v>3.0</v>
       </c>
       <c r="K50" s="36">
@@ -5572,70 +5578,70 @@
       </c>
     </row>
     <row r="51" ht="15.75" customHeight="1">
-      <c r="A51" s="22">
+      <c r="A51" s="21">
         <v>51.0</v>
       </c>
-      <c r="B51" s="23">
+      <c r="B51" s="22">
         <v>46197.0</v>
       </c>
-      <c r="C51" s="22" t="s">
+      <c r="C51" s="21" t="s">
         <v>52</v>
       </c>
-      <c r="D51" s="24" t="s">
-        <v>129</v>
-      </c>
-      <c r="E51" s="46">
-        <v>46024.0</v>
-      </c>
-      <c r="F51" s="41">
+      <c r="D51" s="23" t="s">
+        <v>133</v>
+      </c>
+      <c r="E51" s="24" t="s">
+        <v>57</v>
+      </c>
+      <c r="F51" s="28">
         <v>4.0</v>
       </c>
-      <c r="G51" s="41">
+      <c r="G51" s="28">
         <v>6.5</v>
       </c>
-      <c r="H51" s="41">
+      <c r="H51" s="28">
         <v>7.5</v>
       </c>
-      <c r="I51" s="41">
+      <c r="I51" s="28">
         <v>6.0</v>
       </c>
-      <c r="J51" s="41">
+      <c r="J51" s="28">
         <v>4.0</v>
       </c>
-      <c r="K51" s="29">
+      <c r="K51" s="28">
         <f>IF(COUNT(F51:J51)&lt;5,"",ROUND((F51*Quesitos!$B$3+G51*Quesitos!$B$4+H51*Quesitos!$B$5+I51*Quesitos!$B$6+J51*Quesitos!$B$7)/SUM(Quesitos!$B$3:$B$7),2))</f>
         <v>5.73</v>
       </c>
     </row>
     <row r="52" ht="15.75" customHeight="1">
-      <c r="A52" s="30">
+      <c r="A52" s="29">
         <v>52.0</v>
       </c>
-      <c r="B52" s="31">
+      <c r="B52" s="30">
         <v>46197.0</v>
       </c>
-      <c r="C52" s="30" t="s">
+      <c r="C52" s="29" t="s">
         <v>52</v>
       </c>
-      <c r="D52" s="32" t="s">
-        <v>130</v>
-      </c>
-      <c r="E52" s="44">
-        <v>46025.0</v>
-      </c>
-      <c r="F52" s="42">
+      <c r="D52" s="31" t="s">
+        <v>134</v>
+      </c>
+      <c r="E52" s="32" t="s">
+        <v>88</v>
+      </c>
+      <c r="F52" s="36">
         <v>6.0</v>
       </c>
-      <c r="G52" s="42">
+      <c r="G52" s="36">
         <v>7.5</v>
       </c>
-      <c r="H52" s="42">
+      <c r="H52" s="36">
         <v>3.0</v>
       </c>
-      <c r="I52" s="42">
+      <c r="I52" s="36">
         <v>7.0</v>
       </c>
-      <c r="J52" s="42">
+      <c r="J52" s="36">
         <v>3.0</v>
       </c>
       <c r="K52" s="36">
@@ -5644,142 +5650,142 @@
       </c>
     </row>
     <row r="53" ht="15.75" customHeight="1">
-      <c r="A53" s="22">
+      <c r="A53" s="21">
         <v>49.0</v>
       </c>
-      <c r="B53" s="23">
+      <c r="B53" s="22">
         <v>46197.0</v>
       </c>
-      <c r="C53" s="22" t="s">
+      <c r="C53" s="21" t="s">
         <v>64</v>
       </c>
-      <c r="D53" s="24" t="s">
-        <v>131</v>
-      </c>
-      <c r="E53" s="45" t="s">
-        <v>132</v>
-      </c>
-      <c r="F53" s="41">
+      <c r="D53" s="23" t="s">
+        <v>135</v>
+      </c>
+      <c r="E53" s="24" t="s">
+        <v>136</v>
+      </c>
+      <c r="F53" s="28">
         <v>7.0</v>
       </c>
-      <c r="G53" s="41">
+      <c r="G53" s="28">
         <v>6.5</v>
       </c>
-      <c r="H53" s="41">
+      <c r="H53" s="28">
         <v>6.5</v>
       </c>
-      <c r="I53" s="41">
+      <c r="I53" s="28">
         <v>6.0</v>
       </c>
-      <c r="J53" s="41">
+      <c r="J53" s="28">
         <v>5.0</v>
       </c>
-      <c r="K53" s="29">
+      <c r="K53" s="28">
         <f>IF(COUNT(F53:J53)&lt;5,"",ROUND((F53*Quesitos!$B$3+G53*Quesitos!$B$4+H53*Quesitos!$B$5+I53*Quesitos!$B$6+J53*Quesitos!$B$7)/SUM(Quesitos!$B$3:$B$7),2))</f>
         <v>6.38</v>
       </c>
     </row>
     <row r="54" ht="15.75" customHeight="1">
-      <c r="A54" s="30">
+      <c r="A54" s="29">
         <v>50.0</v>
       </c>
-      <c r="B54" s="31">
+      <c r="B54" s="30">
         <v>46197.0</v>
       </c>
-      <c r="C54" s="30" t="s">
+      <c r="C54" s="29" t="s">
         <v>64</v>
       </c>
-      <c r="D54" s="32" t="s">
-        <v>133</v>
-      </c>
-      <c r="E54" s="44">
-        <v>46057.0</v>
-      </c>
-      <c r="F54" s="42">
-        <v>10.0</v>
-      </c>
-      <c r="G54" s="42">
+      <c r="D54" s="31" t="s">
+        <v>137</v>
+      </c>
+      <c r="E54" s="32" t="s">
+        <v>96</v>
+      </c>
+      <c r="F54" s="41">
         <v>9.0</v>
       </c>
-      <c r="H54" s="42">
+      <c r="G54" s="36">
         <v>9.0</v>
       </c>
-      <c r="I54" s="42">
+      <c r="H54" s="36">
         <v>9.0</v>
       </c>
-      <c r="J54" s="42">
+      <c r="I54" s="36">
+        <v>9.0</v>
+      </c>
+      <c r="J54" s="36">
         <v>9.0</v>
       </c>
       <c r="K54" s="36">
         <f>IF(COUNT(F54:J54)&lt;5,"",ROUND((F54*Quesitos!$B$3+G54*Quesitos!$B$4+H54*Quesitos!$B$5+I54*Quesitos!$B$6+J54*Quesitos!$B$7)/SUM(Quesitos!$B$3:$B$7),2))</f>
-        <v>9.25</v>
+        <v>9</v>
       </c>
     </row>
     <row r="55" ht="15.75" customHeight="1">
-      <c r="A55" s="22">
+      <c r="A55" s="21">
         <v>53.0</v>
       </c>
-      <c r="B55" s="23">
+      <c r="B55" s="22">
         <v>46197.0</v>
       </c>
-      <c r="C55" s="22" t="s">
+      <c r="C55" s="21" t="s">
         <v>60</v>
       </c>
-      <c r="D55" s="24" t="s">
-        <v>134</v>
-      </c>
-      <c r="E55" s="45" t="s">
-        <v>132</v>
-      </c>
-      <c r="F55" s="41">
+      <c r="D55" s="23" t="s">
+        <v>138</v>
+      </c>
+      <c r="E55" s="24" t="s">
+        <v>136</v>
+      </c>
+      <c r="F55" s="28">
         <v>5.0</v>
       </c>
-      <c r="G55" s="41">
+      <c r="G55" s="28">
         <v>8.0</v>
       </c>
-      <c r="H55" s="41">
+      <c r="H55" s="28">
         <v>6.0</v>
       </c>
-      <c r="I55" s="41">
+      <c r="I55" s="28">
         <v>7.0</v>
       </c>
-      <c r="J55" s="41">
+      <c r="J55" s="28">
         <v>7.0</v>
       </c>
-      <c r="K55" s="29">
+      <c r="K55" s="28">
         <f>IF(COUNT(F55:J55)&lt;5,"",ROUND((F55*Quesitos!$B$3+G55*Quesitos!$B$4+H55*Quesitos!$B$5+I55*Quesitos!$B$6+J55*Quesitos!$B$7)/SUM(Quesitos!$B$3:$B$7),2))</f>
         <v>6.55</v>
       </c>
     </row>
     <row r="56" ht="15.75" customHeight="1">
-      <c r="A56" s="30">
+      <c r="A56" s="29">
         <v>54.0</v>
       </c>
-      <c r="B56" s="31">
+      <c r="B56" s="30">
         <v>46197.0</v>
       </c>
-      <c r="C56" s="30" t="s">
+      <c r="C56" s="29" t="s">
         <v>60</v>
       </c>
-      <c r="D56" s="32" t="s">
-        <v>135</v>
-      </c>
-      <c r="E56" s="43" t="s">
+      <c r="D56" s="31" t="s">
+        <v>139</v>
+      </c>
+      <c r="E56" s="32" t="s">
         <v>78</v>
       </c>
-      <c r="F56" s="42">
+      <c r="F56" s="36">
         <v>3.0</v>
       </c>
-      <c r="G56" s="42">
+      <c r="G56" s="36">
         <v>7.5</v>
       </c>
-      <c r="H56" s="42">
+      <c r="H56" s="36">
         <v>8.5</v>
       </c>
-      <c r="I56" s="42">
+      <c r="I56" s="36">
         <v>7.0</v>
       </c>
-      <c r="J56" s="42">
+      <c r="J56" s="36">
         <v>7.0</v>
       </c>
       <c r="K56" s="36">
@@ -5788,70 +5794,70 @@
       </c>
     </row>
     <row r="57" ht="15.75" customHeight="1">
-      <c r="A57" s="22">
+      <c r="A57" s="21">
         <v>55.0</v>
       </c>
-      <c r="B57" s="23">
+      <c r="B57" s="22">
         <v>46198.0</v>
       </c>
-      <c r="C57" s="22" t="s">
+      <c r="C57" s="21" t="s">
         <v>73</v>
       </c>
-      <c r="D57" s="24" t="s">
-        <v>136</v>
-      </c>
-      <c r="E57" s="45" t="s">
-        <v>137</v>
-      </c>
-      <c r="F57" s="41">
+      <c r="D57" s="23" t="s">
+        <v>140</v>
+      </c>
+      <c r="E57" s="24" t="s">
+        <v>141</v>
+      </c>
+      <c r="F57" s="28">
         <v>6.0</v>
       </c>
-      <c r="G57" s="41">
+      <c r="G57" s="28">
         <v>6.0</v>
       </c>
-      <c r="H57" s="41">
+      <c r="H57" s="28">
         <v>5.0</v>
       </c>
-      <c r="I57" s="41">
+      <c r="I57" s="28">
         <v>7.0</v>
       </c>
-      <c r="J57" s="41">
+      <c r="J57" s="28">
         <v>5.0</v>
       </c>
-      <c r="K57" s="29">
+      <c r="K57" s="28">
         <f>IF(COUNT(F57:J57)&lt;5,"",ROUND((F57*Quesitos!$B$3+G57*Quesitos!$B$4+H57*Quesitos!$B$5+I57*Quesitos!$B$6+J57*Quesitos!$B$7)/SUM(Quesitos!$B$3:$B$7),2))</f>
         <v>5.9</v>
       </c>
     </row>
     <row r="58" ht="15.75" customHeight="1">
-      <c r="A58" s="30">
+      <c r="A58" s="29">
         <v>56.0</v>
       </c>
-      <c r="B58" s="31">
+      <c r="B58" s="30">
         <v>46198.0</v>
       </c>
-      <c r="C58" s="30" t="s">
+      <c r="C58" s="29" t="s">
         <v>73</v>
       </c>
-      <c r="D58" s="32" t="s">
-        <v>138</v>
-      </c>
-      <c r="E58" s="44">
-        <v>46024.0</v>
-      </c>
-      <c r="F58" s="42">
+      <c r="D58" s="31" t="s">
+        <v>142</v>
+      </c>
+      <c r="E58" s="32" t="s">
+        <v>57</v>
+      </c>
+      <c r="F58" s="36">
         <v>7.0</v>
       </c>
-      <c r="G58" s="42">
+      <c r="G58" s="36">
         <v>9.0</v>
       </c>
-      <c r="H58" s="42">
+      <c r="H58" s="36">
         <v>10.0</v>
       </c>
-      <c r="I58" s="42">
+      <c r="I58" s="36">
         <v>8.0</v>
       </c>
-      <c r="J58" s="42">
+      <c r="J58" s="36">
         <v>9.0</v>
       </c>
       <c r="K58" s="36">
@@ -5860,70 +5866,70 @@
       </c>
     </row>
     <row r="59" ht="15.75" customHeight="1">
-      <c r="A59" s="22">
+      <c r="A59" s="21">
         <v>57.0</v>
       </c>
-      <c r="B59" s="23">
+      <c r="B59" s="22">
         <v>46198.0</v>
       </c>
-      <c r="C59" s="22" t="s">
+      <c r="C59" s="21" t="s">
         <v>76</v>
       </c>
-      <c r="D59" s="24" t="s">
-        <v>139</v>
-      </c>
-      <c r="E59" s="46">
-        <v>46023.0</v>
-      </c>
-      <c r="F59" s="41">
+      <c r="D59" s="23" t="s">
+        <v>143</v>
+      </c>
+      <c r="E59" s="24" t="s">
+        <v>59</v>
+      </c>
+      <c r="F59" s="28">
         <v>5.0</v>
       </c>
-      <c r="G59" s="41">
+      <c r="G59" s="28">
         <v>5.0</v>
       </c>
-      <c r="H59" s="41">
+      <c r="H59" s="28">
         <v>8.0</v>
       </c>
-      <c r="I59" s="41">
+      <c r="I59" s="28">
         <v>7.0</v>
       </c>
-      <c r="J59" s="41">
+      <c r="J59" s="28">
         <v>6.0</v>
       </c>
-      <c r="K59" s="29">
+      <c r="K59" s="28">
         <f>IF(COUNT(F59:J59)&lt;5,"",ROUND((F59*Quesitos!$B$3+G59*Quesitos!$B$4+H59*Quesitos!$B$5+I59*Quesitos!$B$6+J59*Quesitos!$B$7)/SUM(Quesitos!$B$3:$B$7),2))</f>
         <v>6.1</v>
       </c>
     </row>
     <row r="60" ht="15.75" customHeight="1">
-      <c r="A60" s="30">
+      <c r="A60" s="29">
         <v>58.0</v>
       </c>
-      <c r="B60" s="31">
+      <c r="B60" s="30">
         <v>46198.0</v>
       </c>
-      <c r="C60" s="30" t="s">
+      <c r="C60" s="29" t="s">
         <v>76</v>
       </c>
-      <c r="D60" s="32" t="s">
-        <v>140</v>
-      </c>
-      <c r="E60" s="44">
-        <v>46082.0</v>
-      </c>
-      <c r="F60" s="42">
+      <c r="D60" s="40" t="s">
+        <v>144</v>
+      </c>
+      <c r="E60" s="32" t="s">
+        <v>99</v>
+      </c>
+      <c r="F60" s="36">
         <v>4.0</v>
       </c>
-      <c r="G60" s="42">
+      <c r="G60" s="36">
         <v>6.0</v>
       </c>
-      <c r="H60" s="42">
+      <c r="H60" s="36">
         <v>6.0</v>
       </c>
-      <c r="I60" s="42">
+      <c r="I60" s="36">
         <v>6.0</v>
       </c>
-      <c r="J60" s="42">
+      <c r="J60" s="36">
         <v>5.0</v>
       </c>
       <c r="K60" s="36">
@@ -5932,70 +5938,70 @@
       </c>
     </row>
     <row r="61" ht="15.75" customHeight="1">
-      <c r="A61" s="22">
+      <c r="A61" s="21">
         <v>59.0</v>
       </c>
-      <c r="B61" s="23">
+      <c r="B61" s="22">
         <v>46198.0</v>
       </c>
-      <c r="C61" s="22" t="s">
+      <c r="C61" s="21" t="s">
         <v>55</v>
       </c>
-      <c r="D61" s="24" t="s">
-        <v>141</v>
-      </c>
-      <c r="E61" s="46">
-        <v>46056.0</v>
-      </c>
-      <c r="F61" s="41">
+      <c r="D61" s="23" t="s">
+        <v>145</v>
+      </c>
+      <c r="E61" s="24" t="s">
+        <v>125</v>
+      </c>
+      <c r="F61" s="28">
         <v>8.0</v>
       </c>
-      <c r="G61" s="41">
+      <c r="G61" s="28">
         <v>7.0</v>
       </c>
-      <c r="H61" s="41">
+      <c r="H61" s="28">
         <v>8.5</v>
       </c>
-      <c r="I61" s="41">
+      <c r="I61" s="28">
         <v>5.0</v>
       </c>
-      <c r="J61" s="41">
+      <c r="J61" s="28">
         <v>5.0</v>
       </c>
-      <c r="K61" s="29">
+      <c r="K61" s="28">
         <f>IF(COUNT(F61:J61)&lt;5,"",ROUND((F61*Quesitos!$B$3+G61*Quesitos!$B$4+H61*Quesitos!$B$5+I61*Quesitos!$B$6+J61*Quesitos!$B$7)/SUM(Quesitos!$B$3:$B$7),2))</f>
         <v>6.95</v>
       </c>
     </row>
     <row r="62" ht="15.75" customHeight="1">
-      <c r="A62" s="30">
+      <c r="A62" s="29">
         <v>60.0</v>
       </c>
-      <c r="B62" s="31">
+      <c r="B62" s="30">
         <v>46198.0</v>
       </c>
-      <c r="C62" s="30" t="s">
+      <c r="C62" s="29" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="32" t="s">
-        <v>142</v>
-      </c>
-      <c r="E62" s="43" t="s">
+      <c r="D62" s="31" t="s">
+        <v>146</v>
+      </c>
+      <c r="E62" s="32" t="s">
         <v>83</v>
       </c>
-      <c r="F62" s="42">
+      <c r="F62" s="36">
         <v>2.0</v>
       </c>
-      <c r="G62" s="42">
+      <c r="G62" s="36">
         <v>1.0</v>
       </c>
-      <c r="H62" s="42">
+      <c r="H62" s="36">
         <v>1.0</v>
       </c>
-      <c r="I62" s="42">
+      <c r="I62" s="36">
         <v>1.0</v>
       </c>
-      <c r="J62" s="42">
+      <c r="J62" s="36">
         <v>1.0</v>
       </c>
       <c r="K62" s="36">
@@ -6004,70 +6010,70 @@
       </c>
     </row>
     <row r="63" ht="15.75" customHeight="1">
-      <c r="A63" s="22">
+      <c r="A63" s="21">
         <v>61.0</v>
       </c>
-      <c r="B63" s="23">
+      <c r="B63" s="22">
         <v>46199.0</v>
       </c>
-      <c r="C63" s="22" t="s">
+      <c r="C63" s="21" t="s">
         <v>52</v>
       </c>
-      <c r="D63" s="24" t="s">
-        <v>143</v>
-      </c>
-      <c r="E63" s="46">
-        <v>46113.0</v>
-      </c>
-      <c r="F63" s="41">
+      <c r="D63" s="23" t="s">
+        <v>147</v>
+      </c>
+      <c r="E63" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="F63" s="28">
         <v>9.5</v>
       </c>
-      <c r="G63" s="41">
+      <c r="G63" s="28">
         <v>7.0</v>
       </c>
-      <c r="H63" s="41">
+      <c r="H63" s="28">
         <v>8.0</v>
       </c>
-      <c r="I63" s="41">
+      <c r="I63" s="28">
         <v>6.0</v>
       </c>
-      <c r="J63" s="41">
+      <c r="J63" s="28">
         <v>5.0</v>
       </c>
-      <c r="K63" s="29">
+      <c r="K63" s="28">
         <f>IF(COUNT(F63:J63)&lt;5,"",ROUND((F63*Quesitos!$B$3+G63*Quesitos!$B$4+H63*Quesitos!$B$5+I63*Quesitos!$B$6+J63*Quesitos!$B$7)/SUM(Quesitos!$B$3:$B$7),2))</f>
         <v>7.43</v>
       </c>
     </row>
     <row r="64" ht="15.75" customHeight="1">
-      <c r="A64" s="30">
+      <c r="A64" s="29">
         <v>62.0</v>
       </c>
-      <c r="B64" s="31">
+      <c r="B64" s="30">
         <v>46199.0</v>
       </c>
-      <c r="C64" s="30" t="s">
+      <c r="C64" s="29" t="s">
         <v>52</v>
       </c>
-      <c r="D64" s="32" t="s">
-        <v>144</v>
-      </c>
-      <c r="E64" s="43" t="s">
-        <v>125</v>
-      </c>
-      <c r="F64" s="42">
+      <c r="D64" s="31" t="s">
+        <v>148</v>
+      </c>
+      <c r="E64" s="32" t="s">
+        <v>129</v>
+      </c>
+      <c r="F64" s="36">
         <v>4.0</v>
       </c>
-      <c r="G64" s="42">
+      <c r="G64" s="36">
         <v>8.0</v>
       </c>
-      <c r="H64" s="42">
+      <c r="H64" s="36">
         <v>3.0</v>
       </c>
-      <c r="I64" s="42">
+      <c r="I64" s="36">
         <v>7.0</v>
       </c>
-      <c r="J64" s="42">
+      <c r="J64" s="36">
         <v>5.0</v>
       </c>
       <c r="K64" s="36">
@@ -6076,70 +6082,70 @@
       </c>
     </row>
     <row r="65" ht="15.75" customHeight="1">
-      <c r="A65" s="22">
+      <c r="A65" s="21">
         <v>65.0</v>
       </c>
-      <c r="B65" s="23">
+      <c r="B65" s="22">
         <v>46199.0</v>
       </c>
-      <c r="C65" s="22" t="s">
-        <v>110</v>
-      </c>
-      <c r="D65" s="24" t="s">
-        <v>145</v>
-      </c>
-      <c r="E65" s="45" t="s">
+      <c r="C65" s="21" t="s">
+        <v>112</v>
+      </c>
+      <c r="D65" s="23" t="s">
+        <v>149</v>
+      </c>
+      <c r="E65" s="24" t="s">
         <v>83</v>
       </c>
-      <c r="F65" s="41">
+      <c r="F65" s="28">
         <v>4.0</v>
       </c>
-      <c r="G65" s="41">
+      <c r="G65" s="28">
         <v>5.0</v>
       </c>
-      <c r="H65" s="41">
+      <c r="H65" s="28">
         <v>7.0</v>
       </c>
-      <c r="I65" s="41">
+      <c r="I65" s="28">
         <v>8.0</v>
       </c>
-      <c r="J65" s="41">
+      <c r="J65" s="28">
         <v>10.0</v>
       </c>
-      <c r="K65" s="29">
+      <c r="K65" s="28">
         <f>IF(COUNT(F65:J65)&lt;5,"",ROUND((F65*Quesitos!$B$3+G65*Quesitos!$B$4+H65*Quesitos!$B$5+I65*Quesitos!$B$6+J65*Quesitos!$B$7)/SUM(Quesitos!$B$3:$B$7),2))</f>
         <v>6.25</v>
       </c>
     </row>
     <row r="66" ht="15.75" customHeight="1">
-      <c r="A66" s="30">
+      <c r="A66" s="29">
         <v>66.0</v>
       </c>
-      <c r="B66" s="31">
+      <c r="B66" s="30">
         <v>46199.0</v>
       </c>
-      <c r="C66" s="30" t="s">
-        <v>110</v>
-      </c>
-      <c r="D66" s="32" t="s">
-        <v>146</v>
-      </c>
-      <c r="E66" s="43" t="s">
+      <c r="C66" s="29" t="s">
+        <v>112</v>
+      </c>
+      <c r="D66" s="31" t="s">
+        <v>150</v>
+      </c>
+      <c r="E66" s="32" t="s">
         <v>67</v>
       </c>
-      <c r="F66" s="42">
+      <c r="F66" s="36">
         <v>4.0</v>
       </c>
-      <c r="G66" s="42">
+      <c r="G66" s="36">
         <v>2.0</v>
       </c>
-      <c r="H66" s="42">
+      <c r="H66" s="36">
         <v>5.0</v>
       </c>
-      <c r="I66" s="42">
+      <c r="I66" s="36">
         <v>7.0</v>
       </c>
-      <c r="J66" s="42">
+      <c r="J66" s="36">
         <v>9.0</v>
       </c>
       <c r="K66" s="36">
@@ -6148,70 +6154,70 @@
       </c>
     </row>
     <row r="67" ht="15.75" customHeight="1">
-      <c r="A67" s="22">
+      <c r="A67" s="21">
         <v>63.0</v>
       </c>
-      <c r="B67" s="23">
+      <c r="B67" s="22">
         <v>46200.0</v>
       </c>
-      <c r="C67" s="22" t="s">
-        <v>106</v>
-      </c>
-      <c r="D67" s="24" t="s">
-        <v>147</v>
-      </c>
-      <c r="E67" s="46">
-        <v>46023.0</v>
-      </c>
-      <c r="F67" s="41">
+      <c r="C67" s="21" t="s">
+        <v>108</v>
+      </c>
+      <c r="D67" s="23" t="s">
+        <v>151</v>
+      </c>
+      <c r="E67" s="24" t="s">
+        <v>59</v>
+      </c>
+      <c r="F67" s="28">
         <v>6.5</v>
       </c>
-      <c r="G67" s="41">
+      <c r="G67" s="28">
         <v>7.25</v>
       </c>
-      <c r="H67" s="41">
+      <c r="H67" s="28">
         <v>8.0</v>
       </c>
-      <c r="I67" s="41">
+      <c r="I67" s="28">
         <v>8.0</v>
       </c>
-      <c r="J67" s="41">
+      <c r="J67" s="28">
         <v>6.0</v>
       </c>
-      <c r="K67" s="29">
+      <c r="K67" s="28">
         <f>IF(COUNT(F67:J67)&lt;5,"",ROUND((F67*Quesitos!$B$3+G67*Quesitos!$B$4+H67*Quesitos!$B$5+I67*Quesitos!$B$6+J67*Quesitos!$B$7)/SUM(Quesitos!$B$3:$B$7),2))</f>
         <v>7.24</v>
       </c>
     </row>
     <row r="68" ht="15.75" customHeight="1">
-      <c r="A68" s="30">
+      <c r="A68" s="29">
         <v>64.0</v>
       </c>
-      <c r="B68" s="31">
+      <c r="B68" s="30">
         <v>46200.0</v>
       </c>
-      <c r="C68" s="30" t="s">
-        <v>106</v>
-      </c>
-      <c r="D68" s="32" t="s">
-        <v>148</v>
-      </c>
-      <c r="E68" s="44">
-        <v>46143.0</v>
-      </c>
-      <c r="F68" s="42">
+      <c r="C68" s="29" t="s">
+        <v>108</v>
+      </c>
+      <c r="D68" s="31" t="s">
+        <v>152</v>
+      </c>
+      <c r="E68" s="32" t="s">
+        <v>153</v>
+      </c>
+      <c r="F68" s="36">
         <v>6.0</v>
       </c>
-      <c r="G68" s="42">
+      <c r="G68" s="36">
         <v>9.0</v>
       </c>
-      <c r="H68" s="42">
+      <c r="H68" s="36">
         <v>3.0</v>
       </c>
-      <c r="I68" s="42">
+      <c r="I68" s="36">
         <v>5.0</v>
       </c>
-      <c r="J68" s="42">
+      <c r="J68" s="36">
         <v>5.0</v>
       </c>
       <c r="K68" s="36">
@@ -6220,70 +6226,70 @@
       </c>
     </row>
     <row r="69" ht="15.75" customHeight="1">
-      <c r="A69" s="22">
+      <c r="A69" s="21">
         <v>67.0</v>
       </c>
-      <c r="B69" s="23">
+      <c r="B69" s="22">
         <v>46200.0</v>
       </c>
-      <c r="C69" s="22" t="s">
-        <v>120</v>
-      </c>
-      <c r="D69" s="24" t="s">
-        <v>149</v>
-      </c>
-      <c r="E69" s="45" t="s">
-        <v>137</v>
-      </c>
-      <c r="F69" s="41">
+      <c r="C69" s="21" t="s">
+        <v>122</v>
+      </c>
+      <c r="D69" s="23" t="s">
+        <v>154</v>
+      </c>
+      <c r="E69" s="24" t="s">
+        <v>141</v>
+      </c>
+      <c r="F69" s="28">
         <v>4.0</v>
       </c>
-      <c r="G69" s="41">
+      <c r="G69" s="28">
         <v>7.0</v>
       </c>
-      <c r="H69" s="41">
+      <c r="H69" s="28">
         <v>6.0</v>
       </c>
-      <c r="I69" s="41">
+      <c r="I69" s="28">
         <v>5.0</v>
       </c>
-      <c r="J69" s="41">
+      <c r="J69" s="28">
         <v>4.0</v>
       </c>
-      <c r="K69" s="29">
+      <c r="K69" s="28">
         <f>IF(COUNT(F69:J69)&lt;5,"",ROUND((F69*Quesitos!$B$3+G69*Quesitos!$B$4+H69*Quesitos!$B$5+I69*Quesitos!$B$6+J69*Quesitos!$B$7)/SUM(Quesitos!$B$3:$B$7),2))</f>
         <v>5.35</v>
       </c>
     </row>
     <row r="70" ht="15.75" customHeight="1">
-      <c r="A70" s="30">
+      <c r="A70" s="29">
         <v>68.0</v>
       </c>
-      <c r="B70" s="31">
+      <c r="B70" s="30">
         <v>46200.0</v>
       </c>
-      <c r="C70" s="30" t="s">
-        <v>120</v>
-      </c>
-      <c r="D70" s="32" t="s">
-        <v>150</v>
-      </c>
-      <c r="E70" s="44">
-        <v>46024.0</v>
-      </c>
-      <c r="F70" s="42">
+      <c r="C70" s="29" t="s">
+        <v>122</v>
+      </c>
+      <c r="D70" s="31" t="s">
+        <v>155</v>
+      </c>
+      <c r="E70" s="32" t="s">
+        <v>57</v>
+      </c>
+      <c r="F70" s="36">
         <v>6.0</v>
       </c>
-      <c r="G70" s="42">
+      <c r="G70" s="36">
         <v>8.0</v>
       </c>
-      <c r="H70" s="42">
+      <c r="H70" s="36">
         <v>8.0</v>
       </c>
-      <c r="I70" s="42">
+      <c r="I70" s="36">
         <v>7.0</v>
       </c>
-      <c r="J70" s="42">
+      <c r="J70" s="36">
         <v>6.0</v>
       </c>
       <c r="K70" s="36">
@@ -6292,70 +6298,70 @@
       </c>
     </row>
     <row r="71" ht="15.75" customHeight="1">
-      <c r="A71" s="22">
+      <c r="A71" s="21">
         <v>71.0</v>
       </c>
-      <c r="B71" s="23">
+      <c r="B71" s="22">
         <v>46200.0</v>
       </c>
-      <c r="C71" s="22" t="s">
-        <v>151</v>
-      </c>
-      <c r="D71" s="24" t="s">
-        <v>152</v>
-      </c>
-      <c r="E71" s="45" t="s">
+      <c r="C71" s="21" t="s">
+        <v>156</v>
+      </c>
+      <c r="D71" s="23" t="s">
+        <v>157</v>
+      </c>
+      <c r="E71" s="24" t="s">
         <v>83</v>
       </c>
-      <c r="F71" s="41">
+      <c r="F71" s="28">
         <v>8.25</v>
       </c>
-      <c r="G71" s="41">
+      <c r="G71" s="28">
         <v>9.5</v>
       </c>
-      <c r="H71" s="41">
+      <c r="H71" s="28">
         <v>7.5</v>
       </c>
-      <c r="I71" s="41">
+      <c r="I71" s="28">
         <v>8.0</v>
       </c>
-      <c r="J71" s="41">
+      <c r="J71" s="28">
         <v>5.0</v>
       </c>
-      <c r="K71" s="29">
+      <c r="K71" s="28">
         <f>IF(COUNT(F71:J71)&lt;5,"",ROUND((F71*Quesitos!$B$3+G71*Quesitos!$B$4+H71*Quesitos!$B$5+I71*Quesitos!$B$6+J71*Quesitos!$B$7)/SUM(Quesitos!$B$3:$B$7),2))</f>
         <v>8.04</v>
       </c>
     </row>
     <row r="72" ht="15.75" customHeight="1">
-      <c r="A72" s="30">
+      <c r="A72" s="29">
         <v>72.0</v>
       </c>
-      <c r="B72" s="31">
+      <c r="B72" s="30">
         <v>46200.0</v>
       </c>
-      <c r="C72" s="30" t="s">
-        <v>151</v>
-      </c>
-      <c r="D72" s="32" t="s">
-        <v>153</v>
-      </c>
-      <c r="E72" s="44">
-        <v>46025.0</v>
-      </c>
-      <c r="F72" s="42">
+      <c r="C72" s="29" t="s">
+        <v>156</v>
+      </c>
+      <c r="D72" s="31" t="s">
+        <v>158</v>
+      </c>
+      <c r="E72" s="32" t="s">
+        <v>88</v>
+      </c>
+      <c r="F72" s="36">
         <v>6.25</v>
       </c>
-      <c r="G72" s="42">
+      <c r="G72" s="36">
         <v>7.0</v>
       </c>
-      <c r="H72" s="42">
+      <c r="H72" s="36">
         <v>7.0</v>
       </c>
-      <c r="I72" s="42">
+      <c r="I72" s="36">
         <v>7.5</v>
       </c>
-      <c r="J72" s="42">
+      <c r="J72" s="36">
         <v>10.0</v>
       </c>
       <c r="K72" s="36">
@@ -6364,70 +6370,70 @@
       </c>
     </row>
     <row r="73" ht="15.75" customHeight="1">
-      <c r="A73" s="22">
+      <c r="A73" s="21">
         <v>69.0</v>
       </c>
-      <c r="B73" s="23">
+      <c r="B73" s="22">
         <v>46200.0</v>
       </c>
-      <c r="C73" s="22" t="s">
+      <c r="C73" s="21" t="s">
         <v>55</v>
       </c>
-      <c r="D73" s="24" t="s">
-        <v>154</v>
-      </c>
-      <c r="E73" s="46">
-        <v>46084.0</v>
-      </c>
-      <c r="F73" s="41">
+      <c r="D73" s="23" t="s">
+        <v>159</v>
+      </c>
+      <c r="E73" s="24" t="s">
+        <v>160</v>
+      </c>
+      <c r="F73" s="43">
+        <v>7.0</v>
+      </c>
+      <c r="G73" s="43">
+        <v>10.0</v>
+      </c>
+      <c r="H73" s="28">
+        <v>10.0</v>
+      </c>
+      <c r="I73" s="28">
+        <v>10.0</v>
+      </c>
+      <c r="J73" s="28">
         <v>8.0</v>
       </c>
-      <c r="G73" s="41">
-        <v>10.0</v>
-      </c>
-      <c r="H73" s="41">
-        <v>10.0</v>
-      </c>
-      <c r="I73" s="41">
-        <v>10.0</v>
-      </c>
-      <c r="J73" s="41">
-        <v>8.0</v>
-      </c>
-      <c r="K73" s="29">
+      <c r="K73" s="28">
         <f>IF(COUNT(F73:J73)&lt;5,"",ROUND((F73*Quesitos!$B$3+G73*Quesitos!$B$4+H73*Quesitos!$B$5+I73*Quesitos!$B$6+J73*Quesitos!$B$7)/SUM(Quesitos!$B$3:$B$7),2))</f>
-        <v>9.3</v>
+        <v>9.05</v>
       </c>
     </row>
     <row r="74" ht="15.75" customHeight="1">
-      <c r="A74" s="30">
+      <c r="A74" s="29">
         <v>70.0</v>
       </c>
-      <c r="B74" s="31">
+      <c r="B74" s="30">
         <v>46200.0</v>
       </c>
-      <c r="C74" s="30" t="s">
+      <c r="C74" s="29" t="s">
         <v>55</v>
       </c>
-      <c r="D74" s="32" t="s">
-        <v>155</v>
-      </c>
-      <c r="E74" s="44">
-        <v>46082.0</v>
-      </c>
-      <c r="F74" s="42">
+      <c r="D74" s="31" t="s">
+        <v>161</v>
+      </c>
+      <c r="E74" s="32" t="s">
+        <v>99</v>
+      </c>
+      <c r="F74" s="36">
         <v>7.0</v>
       </c>
-      <c r="G74" s="42">
+      <c r="G74" s="36">
         <v>6.0</v>
       </c>
-      <c r="H74" s="42">
+      <c r="H74" s="36">
         <v>5.0</v>
       </c>
-      <c r="I74" s="42">
+      <c r="I74" s="36">
         <v>7.0</v>
       </c>
-      <c r="J74" s="42">
+      <c r="J74" s="36">
         <v>5.0</v>
       </c>
       <c r="K74" s="36">
@@ -7424,114 +7430,113 @@
     <col customWidth="1" min="6" max="9" width="12.0"/>
     <col customWidth="1" min="10" max="10" width="20.0"/>
     <col customWidth="1" min="11" max="11" width="12.0"/>
-    <col customWidth="1" min="12" max="26" width="8.63"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.75" customHeight="1">
-      <c r="A1" s="20" t="s">
-        <v>156</v>
+      <c r="A1" s="19" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="2" ht="36.0" customHeight="1">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="21" t="s">
+      <c r="B2" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="C2" s="21" t="s">
+      <c r="C2" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="D2" s="21" t="s">
+      <c r="D2" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="E2" s="21" t="s">
+      <c r="E2" s="20" t="s">
         <v>50</v>
       </c>
-      <c r="F2" s="21" t="s">
+      <c r="F2" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="G2" s="21" t="s">
+      <c r="G2" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="H2" s="21" t="s">
+      <c r="H2" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="I2" s="21" t="s">
+      <c r="I2" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="J2" s="21" t="s">
+      <c r="J2" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="K2" s="21" t="s">
+      <c r="K2" s="20" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="22">
+      <c r="A3" s="21">
         <v>73.0</v>
       </c>
-      <c r="B3" s="23">
+      <c r="B3" s="22">
         <v>46201.0</v>
       </c>
-      <c r="C3" s="22" t="s">
+      <c r="C3" s="21" t="s">
         <v>52</v>
       </c>
-      <c r="D3" s="47" t="s">
-        <v>157</v>
-      </c>
-      <c r="E3" s="45" t="s">
+      <c r="D3" s="23" t="s">
+        <v>163</v>
+      </c>
+      <c r="E3" s="24" t="s">
         <v>67</v>
       </c>
-      <c r="F3" s="41">
+      <c r="F3" s="28">
         <v>4.0</v>
       </c>
-      <c r="G3" s="41">
+      <c r="G3" s="28">
         <v>5.0</v>
       </c>
-      <c r="H3" s="41">
+      <c r="H3" s="28">
         <v>7.0</v>
       </c>
-      <c r="I3" s="41">
+      <c r="I3" s="28">
         <v>8.0</v>
       </c>
-      <c r="J3" s="41">
+      <c r="J3" s="28">
         <v>6.0</v>
       </c>
-      <c r="K3" s="29">
+      <c r="K3" s="28">
         <f>IF(COUNT(F3:J3)&lt;5,"",ROUND((F3*Quesitos!$B$3+G3*Quesitos!$B$4+H3*Quesitos!$B$5+I3*Quesitos!$B$6+J3*Quesitos!$B$7)/SUM(Quesitos!$B$3:$B$7),2))</f>
         <v>5.85</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="30">
+      <c r="A4" s="29">
         <v>76.0</v>
       </c>
-      <c r="B4" s="31">
+      <c r="B4" s="30">
         <v>46202.0</v>
       </c>
-      <c r="C4" s="30" t="s">
+      <c r="C4" s="29" t="s">
         <v>70</v>
       </c>
-      <c r="D4" s="48" t="s">
-        <v>158</v>
-      </c>
-      <c r="E4" s="44">
-        <v>46024.0</v>
-      </c>
-      <c r="F4" s="42">
+      <c r="D4" s="31" t="s">
+        <v>164</v>
+      </c>
+      <c r="E4" s="32" t="s">
+        <v>57</v>
+      </c>
+      <c r="F4" s="36">
         <v>5.0</v>
       </c>
-      <c r="G4" s="42">
+      <c r="G4" s="36">
         <v>8.5</v>
       </c>
-      <c r="H4" s="42">
+      <c r="H4" s="36">
         <v>8.0</v>
       </c>
-      <c r="I4" s="42">
+      <c r="I4" s="36">
         <v>10.0</v>
       </c>
-      <c r="J4" s="42">
+      <c r="J4" s="36">
         <v>8.0</v>
       </c>
       <c r="K4" s="36">
@@ -7540,70 +7545,70 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="22">
+      <c r="A5" s="21">
         <v>74.0</v>
       </c>
-      <c r="B5" s="23">
+      <c r="B5" s="22">
         <v>46202.0</v>
       </c>
-      <c r="C5" s="22" t="s">
-        <v>159</v>
-      </c>
-      <c r="D5" s="47" t="s">
-        <v>160</v>
-      </c>
-      <c r="E5" s="45" t="s">
-        <v>161</v>
-      </c>
-      <c r="F5" s="41">
+      <c r="C5" s="21" t="s">
+        <v>165</v>
+      </c>
+      <c r="D5" s="23" t="s">
+        <v>166</v>
+      </c>
+      <c r="E5" s="24" t="s">
+        <v>167</v>
+      </c>
+      <c r="F5" s="28">
         <v>7.0</v>
       </c>
-      <c r="G5" s="41">
+      <c r="G5" s="28">
         <v>7.5</v>
       </c>
-      <c r="H5" s="41">
+      <c r="H5" s="28">
         <v>7.0</v>
       </c>
-      <c r="I5" s="41">
+      <c r="I5" s="28">
         <v>10.0</v>
       </c>
-      <c r="J5" s="41">
+      <c r="J5" s="28">
         <v>10.0</v>
       </c>
-      <c r="K5" s="29">
+      <c r="K5" s="28">
         <f>IF(COUNT(F5:J5)&lt;5,"",ROUND((F5*Quesitos!$B$3+G5*Quesitos!$B$4+H5*Quesitos!$B$5+I5*Quesitos!$B$6+J5*Quesitos!$B$7)/SUM(Quesitos!$B$3:$B$7),2))</f>
         <v>8.03</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="30">
+      <c r="A6" s="29">
         <v>75.0</v>
       </c>
-      <c r="B6" s="31">
+      <c r="B6" s="30">
         <v>46202.0</v>
       </c>
-      <c r="C6" s="30" t="s">
+      <c r="C6" s="29" t="s">
         <v>60</v>
       </c>
-      <c r="D6" s="48" t="s">
-        <v>162</v>
-      </c>
-      <c r="E6" s="43" t="s">
-        <v>163</v>
-      </c>
-      <c r="F6" s="42">
+      <c r="D6" s="31" t="s">
+        <v>168</v>
+      </c>
+      <c r="E6" s="32" t="s">
+        <v>169</v>
+      </c>
+      <c r="F6" s="36">
         <v>6.0</v>
       </c>
-      <c r="G6" s="42">
+      <c r="G6" s="36">
         <v>8.0</v>
       </c>
-      <c r="H6" s="42">
+      <c r="H6" s="36">
         <v>9.0</v>
       </c>
-      <c r="I6" s="42">
+      <c r="I6" s="36">
         <v>10.0</v>
       </c>
-      <c r="J6" s="42">
+      <c r="J6" s="36">
         <v>8.0</v>
       </c>
       <c r="K6" s="36">
@@ -7612,70 +7617,70 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="22">
+      <c r="A7" s="21">
         <v>78.0</v>
       </c>
-      <c r="B7" s="23">
+      <c r="B7" s="22">
         <v>46203.0</v>
       </c>
-      <c r="C7" s="22" t="s">
+      <c r="C7" s="21" t="s">
         <v>70</v>
       </c>
-      <c r="D7" s="47" t="s">
-        <v>164</v>
-      </c>
-      <c r="E7" s="46">
-        <v>46054.0</v>
-      </c>
-      <c r="F7" s="41">
+      <c r="D7" s="23" t="s">
+        <v>170</v>
+      </c>
+      <c r="E7" s="24" t="s">
+        <v>127</v>
+      </c>
+      <c r="F7" s="28">
         <v>6.5</v>
       </c>
-      <c r="G7" s="41">
+      <c r="G7" s="28">
         <v>7.5</v>
       </c>
-      <c r="H7" s="41">
+      <c r="H7" s="28">
         <v>8.0</v>
       </c>
-      <c r="I7" s="41">
+      <c r="I7" s="28">
         <v>8.0</v>
       </c>
-      <c r="J7" s="41">
+      <c r="J7" s="28">
         <v>6.0</v>
       </c>
-      <c r="K7" s="29">
+      <c r="K7" s="28">
         <f>IF(COUNT(F7:J7)&lt;5,"",ROUND((F7*Quesitos!$B$3+G7*Quesitos!$B$4+H7*Quesitos!$B$5+I7*Quesitos!$B$6+J7*Quesitos!$B$7)/SUM(Quesitos!$B$3:$B$7),2))</f>
         <v>7.3</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="30">
+      <c r="A8" s="29">
         <v>77.0</v>
       </c>
-      <c r="B8" s="31">
+      <c r="B8" s="30">
         <v>46203.0</v>
       </c>
-      <c r="C8" s="30" t="s">
-        <v>120</v>
-      </c>
-      <c r="D8" s="48" t="s">
-        <v>165</v>
-      </c>
-      <c r="E8" s="43" t="s">
+      <c r="C8" s="29" t="s">
+        <v>122</v>
+      </c>
+      <c r="D8" s="31" t="s">
+        <v>171</v>
+      </c>
+      <c r="E8" s="32" t="s">
         <v>92</v>
       </c>
-      <c r="F8" s="42">
+      <c r="F8" s="36">
         <v>7.0</v>
       </c>
-      <c r="G8" s="42">
+      <c r="G8" s="36">
         <v>7.5</v>
       </c>
-      <c r="H8" s="42">
+      <c r="H8" s="36">
         <v>4.0</v>
       </c>
-      <c r="I8" s="42">
+      <c r="I8" s="36">
         <v>7.0</v>
       </c>
-      <c r="J8" s="42">
+      <c r="J8" s="36">
         <v>6.0</v>
       </c>
       <c r="K8" s="36">
@@ -7684,70 +7689,70 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="22">
+      <c r="A9" s="21">
         <v>79.0</v>
       </c>
-      <c r="B9" s="23">
+      <c r="B9" s="22">
         <v>46203.0</v>
       </c>
-      <c r="C9" s="22" t="s">
+      <c r="C9" s="21" t="s">
         <v>60</v>
       </c>
-      <c r="D9" s="47" t="s">
-        <v>166</v>
-      </c>
-      <c r="E9" s="45" t="s">
+      <c r="D9" s="23" t="s">
+        <v>172</v>
+      </c>
+      <c r="E9" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="F9" s="41">
+      <c r="F9" s="28">
         <v>8.0</v>
       </c>
-      <c r="G9" s="41">
+      <c r="G9" s="28">
         <v>7.5</v>
       </c>
-      <c r="H9" s="41">
+      <c r="H9" s="28">
         <v>7.0</v>
       </c>
-      <c r="I9" s="41">
+      <c r="I9" s="28">
         <v>7.0</v>
       </c>
-      <c r="J9" s="41">
+      <c r="J9" s="28">
         <v>9.0</v>
       </c>
-      <c r="K9" s="29">
+      <c r="K9" s="28">
         <f>IF(COUNT(F9:J9)&lt;5,"",ROUND((F9*Quesitos!$B$3+G9*Quesitos!$B$4+H9*Quesitos!$B$5+I9*Quesitos!$B$6+J9*Quesitos!$B$7)/SUM(Quesitos!$B$3:$B$7),2))</f>
         <v>7.58</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="30">
+      <c r="A10" s="29">
         <v>80.0</v>
       </c>
-      <c r="B10" s="31">
+      <c r="B10" s="30">
         <v>46204.0</v>
       </c>
-      <c r="C10" s="30" t="s">
+      <c r="C10" s="29" t="s">
         <v>81</v>
       </c>
-      <c r="D10" s="48" t="s">
-        <v>167</v>
-      </c>
-      <c r="E10" s="44">
-        <v>46024.0</v>
-      </c>
-      <c r="F10" s="42">
+      <c r="D10" s="31" t="s">
+        <v>173</v>
+      </c>
+      <c r="E10" s="32" t="s">
+        <v>57</v>
+      </c>
+      <c r="F10" s="36">
         <v>6.0</v>
       </c>
-      <c r="G10" s="42">
+      <c r="G10" s="36">
         <v>7.5</v>
       </c>
-      <c r="H10" s="42">
+      <c r="H10" s="36">
         <v>8.5</v>
       </c>
-      <c r="I10" s="42">
+      <c r="I10" s="36">
         <v>9.0</v>
       </c>
-      <c r="J10" s="42">
+      <c r="J10" s="36">
         <v>8.0</v>
       </c>
       <c r="K10" s="36">
@@ -7756,70 +7761,70 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="22">
+      <c r="A11" s="21">
         <v>82.0</v>
       </c>
-      <c r="B11" s="23">
+      <c r="B11" s="22">
         <v>46204.0</v>
       </c>
-      <c r="C11" s="22" t="s">
+      <c r="C11" s="21" t="s">
         <v>73</v>
       </c>
-      <c r="D11" s="47" t="s">
-        <v>168</v>
-      </c>
-      <c r="E11" s="46">
-        <v>46056.0</v>
-      </c>
-      <c r="F11" s="41">
+      <c r="D11" s="23" t="s">
+        <v>174</v>
+      </c>
+      <c r="E11" s="24" t="s">
+        <v>125</v>
+      </c>
+      <c r="F11" s="28">
         <v>5.0</v>
       </c>
-      <c r="G11" s="41">
+      <c r="G11" s="28">
         <v>10.0</v>
       </c>
-      <c r="H11" s="41">
+      <c r="H11" s="28">
         <v>7.5</v>
       </c>
-      <c r="I11" s="41">
+      <c r="I11" s="28">
         <v>10.0</v>
       </c>
-      <c r="J11" s="41">
+      <c r="J11" s="28">
         <v>6.0</v>
       </c>
-      <c r="K11" s="29">
+      <c r="K11" s="28">
         <f>IF(COUNT(F11:J11)&lt;5,"",ROUND((F11*Quesitos!$B$3+G11*Quesitos!$B$4+H11*Quesitos!$B$5+I11*Quesitos!$B$6+J11*Quesitos!$B$7)/SUM(Quesitos!$B$3:$B$7),2))</f>
         <v>7.85</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="30">
+      <c r="A12" s="29">
         <v>81.0</v>
       </c>
-      <c r="B12" s="31">
+      <c r="B12" s="30">
         <v>46204.0</v>
       </c>
-      <c r="C12" s="30" t="s">
-        <v>110</v>
-      </c>
-      <c r="D12" s="48" t="s">
-        <v>169</v>
-      </c>
-      <c r="E12" s="43" t="s">
+      <c r="C12" s="29" t="s">
+        <v>112</v>
+      </c>
+      <c r="D12" s="31" t="s">
+        <v>175</v>
+      </c>
+      <c r="E12" s="32" t="s">
         <v>54</v>
       </c>
-      <c r="F12" s="42">
+      <c r="F12" s="36">
         <v>6.0</v>
       </c>
-      <c r="G12" s="42">
+      <c r="G12" s="36">
         <v>6.0</v>
       </c>
-      <c r="H12" s="42">
+      <c r="H12" s="36">
         <v>6.0</v>
       </c>
-      <c r="I12" s="42">
+      <c r="I12" s="36">
         <v>6.0</v>
       </c>
-      <c r="J12" s="42">
+      <c r="J12" s="36">
         <v>7.0</v>
       </c>
       <c r="K12" s="36">
@@ -7828,70 +7833,70 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="22">
+      <c r="A13" s="21">
         <v>84.0</v>
       </c>
-      <c r="B13" s="23">
+      <c r="B13" s="22">
         <v>46205.0</v>
       </c>
-      <c r="C13" s="22" t="s">
+      <c r="C13" s="21" t="s">
         <v>52</v>
       </c>
-      <c r="D13" s="47" t="s">
-        <v>170</v>
-      </c>
-      <c r="E13" s="45" t="s">
+      <c r="D13" s="23" t="s">
+        <v>176</v>
+      </c>
+      <c r="E13" s="24" t="s">
         <v>92</v>
       </c>
-      <c r="F13" s="41">
+      <c r="F13" s="28">
         <v>6.0</v>
       </c>
-      <c r="G13" s="41">
+      <c r="G13" s="28">
         <v>7.0</v>
       </c>
-      <c r="H13" s="41">
+      <c r="H13" s="28">
         <v>6.0</v>
       </c>
-      <c r="I13" s="41">
+      <c r="I13" s="28">
         <v>5.0</v>
       </c>
-      <c r="J13" s="41">
+      <c r="J13" s="28">
         <v>6.0</v>
       </c>
-      <c r="K13" s="29">
+      <c r="K13" s="28">
         <f>IF(COUNT(F13:J13)&lt;5,"",ROUND((F13*Quesitos!$B$3+G13*Quesitos!$B$4+H13*Quesitos!$B$5+I13*Quesitos!$B$6+J13*Quesitos!$B$7)/SUM(Quesitos!$B$3:$B$7),2))</f>
         <v>6.05</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="30">
+      <c r="A14" s="29">
         <v>83.0</v>
       </c>
-      <c r="B14" s="31">
+      <c r="B14" s="30">
         <v>46205.0</v>
       </c>
-      <c r="C14" s="30" t="s">
+      <c r="C14" s="29" t="s">
         <v>76</v>
       </c>
-      <c r="D14" s="48" t="s">
-        <v>171</v>
-      </c>
-      <c r="E14" s="44">
-        <v>46024.0</v>
-      </c>
-      <c r="F14" s="42">
+      <c r="D14" s="31" t="s">
+        <v>177</v>
+      </c>
+      <c r="E14" s="32" t="s">
+        <v>57</v>
+      </c>
+      <c r="F14" s="36">
         <v>5.0</v>
       </c>
-      <c r="G14" s="42">
+      <c r="G14" s="36">
         <v>10.0</v>
       </c>
-      <c r="H14" s="42">
+      <c r="H14" s="36">
         <v>10.0</v>
       </c>
-      <c r="I14" s="42">
+      <c r="I14" s="36">
         <v>10.0</v>
       </c>
-      <c r="J14" s="42">
+      <c r="J14" s="36">
         <v>9.0</v>
       </c>
       <c r="K14" s="36">
@@ -7900,70 +7905,70 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="22">
+      <c r="A15" s="21">
         <v>85.0</v>
       </c>
-      <c r="B15" s="23">
+      <c r="B15" s="22">
         <v>46206.0</v>
       </c>
-      <c r="C15" s="22" t="s">
-        <v>106</v>
-      </c>
-      <c r="D15" s="47" t="s">
-        <v>172</v>
-      </c>
-      <c r="E15" s="45" t="s">
+      <c r="C15" s="21" t="s">
+        <v>108</v>
+      </c>
+      <c r="D15" s="23" t="s">
+        <v>178</v>
+      </c>
+      <c r="E15" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="F15" s="41">
+      <c r="F15" s="28">
         <v>6.0</v>
       </c>
-      <c r="G15" s="41">
+      <c r="G15" s="28">
         <v>6.5</v>
       </c>
-      <c r="H15" s="41">
+      <c r="H15" s="28">
         <v>6.0</v>
       </c>
-      <c r="I15" s="41">
+      <c r="I15" s="28">
         <v>6.0</v>
       </c>
-      <c r="J15" s="41">
+      <c r="J15" s="28">
         <v>7.0</v>
       </c>
-      <c r="K15" s="29">
+      <c r="K15" s="28">
         <f>IF(COUNT(F15:J15)&lt;5,"",ROUND((F15*Quesitos!$B$3+G15*Quesitos!$B$4+H15*Quesitos!$B$5+I15*Quesitos!$B$6+J15*Quesitos!$B$7)/SUM(Quesitos!$B$3:$B$7),2))</f>
         <v>6.23</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="30">
+      <c r="A16" s="29">
         <v>88.0</v>
       </c>
-      <c r="B16" s="31">
+      <c r="B16" s="30">
         <v>46206.0</v>
       </c>
-      <c r="C16" s="30" t="s">
-        <v>173</v>
-      </c>
-      <c r="D16" s="48" t="s">
-        <v>174</v>
-      </c>
-      <c r="E16" s="43" t="s">
-        <v>175</v>
-      </c>
-      <c r="F16" s="42">
+      <c r="C16" s="29" t="s">
+        <v>179</v>
+      </c>
+      <c r="D16" s="31" t="s">
+        <v>180</v>
+      </c>
+      <c r="E16" s="32" t="s">
+        <v>181</v>
+      </c>
+      <c r="F16" s="36">
         <v>5.0</v>
       </c>
-      <c r="G16" s="42">
+      <c r="G16" s="36">
         <v>7.0</v>
       </c>
-      <c r="H16" s="42">
+      <c r="H16" s="36">
         <v>8.0</v>
       </c>
-      <c r="I16" s="42">
+      <c r="I16" s="36">
         <v>8.0</v>
       </c>
-      <c r="J16" s="42">
+      <c r="J16" s="36">
         <v>8.0</v>
       </c>
       <c r="K16" s="36">
@@ -7972,70 +7977,70 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="22">
+      <c r="A17" s="21">
         <v>86.0</v>
       </c>
-      <c r="B17" s="23">
+      <c r="B17" s="22">
         <v>46206.0</v>
       </c>
-      <c r="C17" s="22" t="s">
+      <c r="C17" s="21" t="s">
         <v>64</v>
       </c>
-      <c r="D17" s="47" t="s">
-        <v>176</v>
-      </c>
-      <c r="E17" s="46">
-        <v>46056.0</v>
-      </c>
-      <c r="F17" s="41">
-        <v>7.0</v>
-      </c>
-      <c r="G17" s="41">
+      <c r="D17" s="23" t="s">
+        <v>182</v>
+      </c>
+      <c r="E17" s="24" t="s">
+        <v>125</v>
+      </c>
+      <c r="F17" s="43">
+        <v>8.5</v>
+      </c>
+      <c r="G17" s="28">
         <v>10.0</v>
       </c>
-      <c r="H17" s="41">
+      <c r="H17" s="28">
         <v>10.0</v>
       </c>
-      <c r="I17" s="41">
+      <c r="I17" s="28">
         <v>10.0</v>
       </c>
-      <c r="J17" s="41">
+      <c r="J17" s="28">
         <v>10.0</v>
       </c>
-      <c r="K17" s="29">
+      <c r="K17" s="28">
         <f>IF(COUNT(F17:J17)&lt;5,"",ROUND((F17*Quesitos!$B$3+G17*Quesitos!$B$4+H17*Quesitos!$B$5+I17*Quesitos!$B$6+J17*Quesitos!$B$7)/SUM(Quesitos!$B$3:$B$7),2))</f>
-        <v>9.25</v>
+        <v>9.63</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="30">
+      <c r="A18" s="29">
         <v>87.0</v>
       </c>
-      <c r="B18" s="31">
+      <c r="B18" s="30">
         <v>46206.0</v>
       </c>
-      <c r="C18" s="30" t="s">
-        <v>177</v>
-      </c>
-      <c r="D18" s="48" t="s">
-        <v>178</v>
-      </c>
-      <c r="E18" s="43" t="s">
+      <c r="C18" s="29" t="s">
+        <v>183</v>
+      </c>
+      <c r="D18" s="31" t="s">
+        <v>184</v>
+      </c>
+      <c r="E18" s="32" t="s">
         <v>78</v>
       </c>
-      <c r="F18" s="42">
+      <c r="F18" s="36">
         <v>5.0</v>
       </c>
-      <c r="G18" s="42">
+      <c r="G18" s="36">
         <v>6.0</v>
       </c>
-      <c r="H18" s="42">
+      <c r="H18" s="36">
         <v>7.5</v>
       </c>
-      <c r="I18" s="42">
+      <c r="I18" s="36">
         <v>7.0</v>
       </c>
-      <c r="J18" s="42">
+      <c r="J18" s="36">
         <v>5.0</v>
       </c>
       <c r="K18" s="36">
@@ -9082,114 +9087,113 @@
     <col customWidth="1" min="6" max="9" width="12.0"/>
     <col customWidth="1" min="10" max="10" width="20.0"/>
     <col customWidth="1" min="11" max="11" width="12.0"/>
-    <col customWidth="1" min="12" max="26" width="8.63"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.75" customHeight="1">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="19" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="2" ht="36.0" customHeight="1">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="21" t="s">
+      <c r="B2" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="C2" s="21" t="s">
+      <c r="C2" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="D2" s="21" t="s">
+      <c r="D2" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="E2" s="21" t="s">
+      <c r="E2" s="20" t="s">
         <v>50</v>
       </c>
-      <c r="F2" s="21" t="s">
+      <c r="F2" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="G2" s="21" t="s">
+      <c r="G2" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="H2" s="21" t="s">
+      <c r="H2" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="I2" s="21" t="s">
+      <c r="I2" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="J2" s="21" t="s">
+      <c r="J2" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="K2" s="21" t="s">
+      <c r="K2" s="20" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="22">
+      <c r="A3" s="21">
         <v>90.0</v>
       </c>
-      <c r="B3" s="23">
+      <c r="B3" s="22">
         <v>46207.0</v>
       </c>
-      <c r="C3" s="22" t="s">
+      <c r="C3" s="21" t="s">
         <v>70</v>
       </c>
-      <c r="D3" s="47" t="s">
-        <v>179</v>
-      </c>
-      <c r="E3" s="45" t="s">
-        <v>132</v>
-      </c>
-      <c r="F3" s="41">
+      <c r="D3" s="23" t="s">
+        <v>185</v>
+      </c>
+      <c r="E3" s="24" t="s">
+        <v>136</v>
+      </c>
+      <c r="F3" s="28">
         <v>7.0</v>
       </c>
-      <c r="G3" s="41">
+      <c r="G3" s="28">
         <v>8.5</v>
       </c>
-      <c r="H3" s="41">
+      <c r="H3" s="28">
         <v>8.0</v>
       </c>
-      <c r="I3" s="41">
+      <c r="I3" s="28">
         <v>6.0</v>
       </c>
-      <c r="J3" s="41">
+      <c r="J3" s="28">
         <v>7.0</v>
       </c>
-      <c r="K3" s="29">
+      <c r="K3" s="28">
         <f>IF(COUNT(F3:J3)&lt;5,"",ROUND((F3*Quesitos!$B$3+G3*Quesitos!$B$4+H3*Quesitos!$B$5+I3*Quesitos!$B$6+J3*Quesitos!$B$7)/SUM(Quesitos!$B$3:$B$7),2))</f>
         <v>7.38</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="30">
+      <c r="A4" s="29">
         <v>89.0</v>
       </c>
-      <c r="B4" s="31">
+      <c r="B4" s="30">
         <v>46207.0</v>
       </c>
-      <c r="C4" s="30" t="s">
-        <v>120</v>
-      </c>
-      <c r="D4" s="48" t="s">
-        <v>180</v>
-      </c>
-      <c r="E4" s="43" t="s">
+      <c r="C4" s="29" t="s">
+        <v>122</v>
+      </c>
+      <c r="D4" s="31" t="s">
+        <v>186</v>
+      </c>
+      <c r="E4" s="32" t="s">
         <v>67</v>
       </c>
-      <c r="F4" s="42">
+      <c r="F4" s="36">
         <v>9.0</v>
       </c>
-      <c r="G4" s="42">
+      <c r="G4" s="36">
         <v>9.5</v>
       </c>
-      <c r="H4" s="42">
+      <c r="H4" s="36">
         <v>7.0</v>
       </c>
-      <c r="I4" s="42">
+      <c r="I4" s="36">
         <v>8.0</v>
       </c>
-      <c r="J4" s="42">
+      <c r="J4" s="36">
         <v>8.0</v>
       </c>
       <c r="K4" s="36">
@@ -9198,70 +9202,70 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="22">
+      <c r="A5" s="21">
         <v>91.0</v>
       </c>
-      <c r="B5" s="23">
+      <c r="B5" s="22">
         <v>46208.0</v>
       </c>
-      <c r="C5" s="22" t="s">
+      <c r="C5" s="21" t="s">
         <v>73</v>
       </c>
-      <c r="D5" s="47" t="s">
-        <v>181</v>
-      </c>
-      <c r="E5" s="46">
-        <v>46054.0</v>
-      </c>
-      <c r="F5" s="41">
+      <c r="D5" s="23" t="s">
+        <v>187</v>
+      </c>
+      <c r="E5" s="24" t="s">
+        <v>127</v>
+      </c>
+      <c r="F5" s="28">
         <v>6.0</v>
       </c>
-      <c r="G5" s="41">
+      <c r="G5" s="28">
         <v>8.0</v>
       </c>
-      <c r="H5" s="41">
+      <c r="H5" s="28">
         <v>9.0</v>
       </c>
-      <c r="I5" s="41">
+      <c r="I5" s="28">
         <v>8.5</v>
       </c>
-      <c r="J5" s="41">
+      <c r="J5" s="28">
         <v>9.0</v>
       </c>
-      <c r="K5" s="29">
+      <c r="K5" s="28">
         <f>IF(COUNT(F5:J5)&lt;5,"",ROUND((F5*Quesitos!$B$3+G5*Quesitos!$B$4+H5*Quesitos!$B$5+I5*Quesitos!$B$6+J5*Quesitos!$B$7)/SUM(Quesitos!$B$3:$B$7),2))</f>
         <v>7.9</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="30">
+      <c r="A6" s="29">
         <v>92.0</v>
       </c>
-      <c r="B6" s="31">
+      <c r="B6" s="30">
         <v>46208.0</v>
       </c>
-      <c r="C6" s="30" t="s">
-        <v>110</v>
-      </c>
-      <c r="D6" s="48" t="s">
-        <v>182</v>
-      </c>
-      <c r="E6" s="44">
-        <v>46056.0</v>
-      </c>
-      <c r="F6" s="42">
+      <c r="C6" s="29" t="s">
+        <v>112</v>
+      </c>
+      <c r="D6" s="31" t="s">
+        <v>188</v>
+      </c>
+      <c r="E6" s="32" t="s">
+        <v>125</v>
+      </c>
+      <c r="F6" s="36">
         <v>7.0</v>
       </c>
-      <c r="G6" s="42">
+      <c r="G6" s="36">
         <v>10.0</v>
       </c>
-      <c r="H6" s="42">
+      <c r="H6" s="36">
         <v>9.5</v>
       </c>
-      <c r="I6" s="42">
+      <c r="I6" s="36">
         <v>10.0</v>
       </c>
-      <c r="J6" s="42">
+      <c r="J6" s="36">
         <v>10.0</v>
       </c>
       <c r="K6" s="36">
@@ -9270,70 +9274,70 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="22">
+      <c r="A7" s="21">
         <v>93.0</v>
       </c>
-      <c r="B7" s="23">
+      <c r="B7" s="22">
         <v>46209.0</v>
       </c>
-      <c r="C7" s="22" t="s">
+      <c r="C7" s="21" t="s">
         <v>52</v>
       </c>
-      <c r="D7" s="47" t="s">
-        <v>183</v>
-      </c>
-      <c r="E7" s="45" t="s">
+      <c r="D7" s="23" t="s">
+        <v>189</v>
+      </c>
+      <c r="E7" s="24" t="s">
         <v>67</v>
       </c>
-      <c r="F7" s="41">
+      <c r="F7" s="28">
         <v>4.0</v>
       </c>
-      <c r="G7" s="41">
+      <c r="G7" s="28">
         <v>5.0</v>
       </c>
-      <c r="H7" s="41">
+      <c r="H7" s="28">
         <v>6.5</v>
       </c>
-      <c r="I7" s="41">
+      <c r="I7" s="28">
         <v>9.0</v>
       </c>
-      <c r="J7" s="41">
+      <c r="J7" s="28">
         <v>6.0</v>
       </c>
-      <c r="K7" s="29">
+      <c r="K7" s="28">
         <f>IF(COUNT(F7:J7)&lt;5,"",ROUND((F7*Quesitos!$B$3+G7*Quesitos!$B$4+H7*Quesitos!$B$5+I7*Quesitos!$B$6+J7*Quesitos!$B$7)/SUM(Quesitos!$B$3:$B$7),2))</f>
         <v>5.95</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="30">
+      <c r="A8" s="29">
         <v>94.0</v>
       </c>
-      <c r="B8" s="31">
+      <c r="B8" s="30">
         <v>46209.0</v>
       </c>
-      <c r="C8" s="30" t="s">
-        <v>110</v>
-      </c>
-      <c r="D8" s="48" t="s">
-        <v>184</v>
-      </c>
-      <c r="E8" s="44">
-        <v>46113.0</v>
-      </c>
-      <c r="F8" s="42">
+      <c r="C8" s="29" t="s">
+        <v>112</v>
+      </c>
+      <c r="D8" s="31" t="s">
+        <v>190</v>
+      </c>
+      <c r="E8" s="32" t="s">
+        <v>90</v>
+      </c>
+      <c r="F8" s="36">
         <v>7.5</v>
       </c>
-      <c r="G8" s="42">
+      <c r="G8" s="36">
         <v>6.0</v>
       </c>
-      <c r="H8" s="42">
+      <c r="H8" s="36">
         <v>8.0</v>
       </c>
-      <c r="I8" s="42">
+      <c r="I8" s="36">
         <v>6.0</v>
       </c>
-      <c r="J8" s="42">
+      <c r="J8" s="36">
         <v>9.0</v>
       </c>
       <c r="K8" s="36">
@@ -9342,70 +9346,70 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="22">
+      <c r="A9" s="21">
         <v>95.0</v>
       </c>
-      <c r="B9" s="23">
+      <c r="B9" s="22">
         <v>46210.0</v>
       </c>
-      <c r="C9" s="22" t="s">
+      <c r="C9" s="21" t="s">
         <v>81</v>
       </c>
-      <c r="D9" s="47" t="s">
-        <v>185</v>
-      </c>
-      <c r="E9" s="46">
-        <v>46056.0</v>
-      </c>
-      <c r="F9" s="41">
+      <c r="D9" s="23" t="s">
+        <v>191</v>
+      </c>
+      <c r="E9" s="24" t="s">
+        <v>125</v>
+      </c>
+      <c r="F9" s="28">
         <v>7.5</v>
       </c>
-      <c r="G9" s="41">
+      <c r="G9" s="28">
         <v>10.0</v>
       </c>
-      <c r="H9" s="41">
+      <c r="H9" s="28">
         <v>9.0</v>
       </c>
-      <c r="I9" s="41">
+      <c r="I9" s="28">
         <v>10.0</v>
       </c>
-      <c r="J9" s="41">
+      <c r="J9" s="28">
         <v>10.0</v>
       </c>
-      <c r="K9" s="29">
+      <c r="K9" s="28">
         <f>IF(COUNT(F9:J9)&lt;5,"",ROUND((F9*Quesitos!$B$3+G9*Quesitos!$B$4+H9*Quesitos!$B$5+I9*Quesitos!$B$6+J9*Quesitos!$B$7)/SUM(Quesitos!$B$3:$B$7),2))</f>
         <v>9.18</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="30">
+      <c r="A10" s="29">
         <v>96.0</v>
       </c>
-      <c r="B10" s="31">
+      <c r="B10" s="30">
         <v>46210.0</v>
       </c>
-      <c r="C10" s="30" t="s">
+      <c r="C10" s="29" t="s">
         <v>73</v>
       </c>
-      <c r="D10" s="48" t="s">
-        <v>186</v>
-      </c>
-      <c r="E10" s="43" t="s">
-        <v>187</v>
-      </c>
-      <c r="F10" s="42">
+      <c r="D10" s="31" t="s">
+        <v>192</v>
+      </c>
+      <c r="E10" s="32" t="s">
+        <v>193</v>
+      </c>
+      <c r="F10" s="36">
         <v>5.0</v>
       </c>
-      <c r="G10" s="42">
+      <c r="G10" s="36">
         <v>6.0</v>
       </c>
-      <c r="H10" s="42">
+      <c r="H10" s="36">
         <v>10.0</v>
       </c>
-      <c r="I10" s="42">
+      <c r="I10" s="36">
         <v>8.0</v>
       </c>
-      <c r="J10" s="42">
+      <c r="J10" s="36">
         <v>7.0</v>
       </c>
       <c r="K10" s="36">
@@ -10452,114 +10456,113 @@
     <col customWidth="1" min="6" max="9" width="12.0"/>
     <col customWidth="1" min="10" max="10" width="20.0"/>
     <col customWidth="1" min="11" max="11" width="12.0"/>
-    <col customWidth="1" min="12" max="26" width="8.63"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.75" customHeight="1">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="19" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="2" ht="36.0" customHeight="1">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="21" t="s">
+      <c r="B2" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="C2" s="21" t="s">
+      <c r="C2" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="D2" s="21" t="s">
+      <c r="D2" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="E2" s="21" t="s">
+      <c r="E2" s="20" t="s">
         <v>50</v>
       </c>
-      <c r="F2" s="21" t="s">
+      <c r="F2" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="G2" s="21" t="s">
+      <c r="G2" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="H2" s="21" t="s">
+      <c r="H2" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="I2" s="21" t="s">
+      <c r="I2" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="J2" s="21" t="s">
+      <c r="J2" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="K2" s="21" t="s">
+      <c r="K2" s="20" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="22">
+      <c r="A3" s="21">
         <v>97.0</v>
       </c>
-      <c r="B3" s="23">
+      <c r="B3" s="22">
         <v>46212.0</v>
       </c>
-      <c r="C3" s="22" t="s">
+      <c r="C3" s="21" t="s">
         <v>73</v>
       </c>
-      <c r="D3" s="47" t="s">
-        <v>188</v>
-      </c>
-      <c r="E3" s="45" t="s">
+      <c r="D3" s="23" t="s">
+        <v>194</v>
+      </c>
+      <c r="E3" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="F3" s="41">
+      <c r="F3" s="28">
         <v>6.0</v>
       </c>
-      <c r="G3" s="41">
+      <c r="G3" s="28">
         <v>7.5</v>
       </c>
-      <c r="H3" s="41">
+      <c r="H3" s="28">
         <v>6.0</v>
       </c>
-      <c r="I3" s="41">
+      <c r="I3" s="28">
         <v>5.0</v>
       </c>
-      <c r="J3" s="41">
+      <c r="J3" s="28">
         <v>5.0</v>
       </c>
-      <c r="K3" s="29">
+      <c r="K3" s="28">
         <f>IF(COUNT(F3:J3)&lt;5,"",ROUND((F3*Quesitos!$B$3+G3*Quesitos!$B$4+H3*Quesitos!$B$5+I3*Quesitos!$B$6+J3*Quesitos!$B$7)/SUM(Quesitos!$B$3:$B$7),2))</f>
         <v>6.08</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="30">
+      <c r="A4" s="29">
         <v>98.0</v>
       </c>
-      <c r="B4" s="31">
+      <c r="B4" s="30">
         <v>46213.0</v>
       </c>
-      <c r="C4" s="30" t="s">
+      <c r="C4" s="29" t="s">
         <v>52</v>
       </c>
-      <c r="D4" s="48" t="s">
-        <v>189</v>
-      </c>
-      <c r="E4" s="44">
-        <v>46024.0</v>
-      </c>
-      <c r="F4" s="42">
+      <c r="D4" s="31" t="s">
+        <v>195</v>
+      </c>
+      <c r="E4" s="32" t="s">
+        <v>57</v>
+      </c>
+      <c r="F4" s="36">
         <v>6.0</v>
       </c>
-      <c r="G4" s="42">
+      <c r="G4" s="36">
         <v>8.0</v>
       </c>
-      <c r="H4" s="42">
+      <c r="H4" s="36">
         <v>8.0</v>
       </c>
-      <c r="I4" s="42">
+      <c r="I4" s="36">
         <v>9.5</v>
       </c>
-      <c r="J4" s="42">
+      <c r="J4" s="36">
         <v>6.0</v>
       </c>
       <c r="K4" s="36">
@@ -10568,70 +10571,70 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="22">
+      <c r="A5" s="21">
         <v>99.0</v>
       </c>
-      <c r="B5" s="23">
+      <c r="B5" s="22">
         <v>46214.0</v>
       </c>
-      <c r="C5" s="22" t="s">
-        <v>120</v>
-      </c>
-      <c r="D5" s="47" t="s">
-        <v>190</v>
-      </c>
-      <c r="E5" s="46">
-        <v>46054.0</v>
-      </c>
-      <c r="F5" s="41">
+      <c r="C5" s="21" t="s">
+        <v>122</v>
+      </c>
+      <c r="D5" s="23" t="s">
+        <v>196</v>
+      </c>
+      <c r="E5" s="24" t="s">
+        <v>127</v>
+      </c>
+      <c r="F5" s="28">
         <v>7.0</v>
       </c>
-      <c r="G5" s="41">
+      <c r="G5" s="28">
         <v>8.0</v>
       </c>
-      <c r="H5" s="41">
+      <c r="H5" s="28">
         <v>9.0</v>
       </c>
-      <c r="I5" s="41">
+      <c r="I5" s="28">
         <v>9.0</v>
       </c>
-      <c r="J5" s="41">
+      <c r="J5" s="28">
         <v>6.0</v>
       </c>
-      <c r="K5" s="29">
+      <c r="K5" s="28">
         <f>IF(COUNT(F5:J5)&lt;5,"",ROUND((F5*Quesitos!$B$3+G5*Quesitos!$B$4+H5*Quesitos!$B$5+I5*Quesitos!$B$6+J5*Quesitos!$B$7)/SUM(Quesitos!$B$3:$B$7),2))</f>
         <v>7.95</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="30">
+      <c r="A6" s="29">
         <v>100.0</v>
       </c>
-      <c r="B6" s="31">
+      <c r="B6" s="30">
         <v>46214.0</v>
       </c>
-      <c r="C6" s="30" t="s">
+      <c r="C6" s="29" t="s">
         <v>60</v>
       </c>
-      <c r="D6" s="48" t="s">
-        <v>191</v>
-      </c>
-      <c r="E6" s="44">
-        <v>46025.0</v>
-      </c>
-      <c r="F6" s="42">
+      <c r="D6" s="31" t="s">
+        <v>197</v>
+      </c>
+      <c r="E6" s="32" t="s">
+        <v>88</v>
+      </c>
+      <c r="F6" s="36">
         <v>6.0</v>
       </c>
-      <c r="G6" s="42">
+      <c r="G6" s="36">
         <v>9.0</v>
       </c>
-      <c r="H6" s="42">
+      <c r="H6" s="36">
         <v>7.5</v>
       </c>
-      <c r="I6" s="42">
+      <c r="I6" s="36">
         <v>9.0</v>
       </c>
-      <c r="J6" s="42">
+      <c r="J6" s="36">
         <v>6.0</v>
       </c>
       <c r="K6" s="36">
@@ -11678,114 +11681,113 @@
     <col customWidth="1" min="6" max="9" width="12.0"/>
     <col customWidth="1" min="10" max="10" width="20.0"/>
     <col customWidth="1" min="11" max="11" width="12.0"/>
-    <col customWidth="1" min="12" max="26" width="8.63"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.75" customHeight="1">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="19" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="2" ht="36.0" customHeight="1">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="21" t="s">
+      <c r="B2" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="C2" s="21" t="s">
+      <c r="C2" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="D2" s="21" t="s">
+      <c r="D2" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="E2" s="21" t="s">
+      <c r="E2" s="20" t="s">
         <v>50</v>
       </c>
-      <c r="F2" s="21" t="s">
+      <c r="F2" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="G2" s="21" t="s">
+      <c r="G2" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="H2" s="21" t="s">
+      <c r="H2" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="I2" s="21" t="s">
+      <c r="I2" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="J2" s="21" t="s">
+      <c r="J2" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="K2" s="21" t="s">
+      <c r="K2" s="20" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="22">
+      <c r="A3" s="21">
         <v>101.0</v>
       </c>
-      <c r="B3" s="23">
+      <c r="B3" s="22">
         <v>46217.0</v>
       </c>
-      <c r="C3" s="22" t="s">
+      <c r="C3" s="21" t="s">
         <v>52</v>
       </c>
-      <c r="D3" s="47" t="s">
-        <v>192</v>
-      </c>
-      <c r="E3" s="45" t="s">
-        <v>137</v>
-      </c>
-      <c r="F3" s="41">
+      <c r="D3" s="23" t="s">
+        <v>198</v>
+      </c>
+      <c r="E3" s="24" t="s">
+        <v>141</v>
+      </c>
+      <c r="F3" s="28">
         <v>6.0</v>
       </c>
-      <c r="G3" s="41">
+      <c r="G3" s="28">
         <v>7.0</v>
       </c>
-      <c r="H3" s="41">
+      <c r="H3" s="28">
         <v>8.0</v>
       </c>
-      <c r="I3" s="41">
+      <c r="I3" s="28">
         <v>9.0</v>
       </c>
-      <c r="J3" s="41">
+      <c r="J3" s="28">
         <v>6.0</v>
       </c>
-      <c r="K3" s="29">
+      <c r="K3" s="28">
         <f>IF(COUNT(F3:J3)&lt;5,"",ROUND((F3*Quesitos!$B$3+G3*Quesitos!$B$4+H3*Quesitos!$B$5+I3*Quesitos!$B$6+J3*Quesitos!$B$7)/SUM(Quesitos!$B$3:$B$7),2))</f>
         <v>7.25</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="30">
+      <c r="A4" s="29">
         <v>102.0</v>
       </c>
-      <c r="B4" s="31">
+      <c r="B4" s="30">
         <v>46218.0</v>
       </c>
-      <c r="C4" s="30" t="s">
+      <c r="C4" s="29" t="s">
         <v>52</v>
       </c>
-      <c r="D4" s="48" t="s">
-        <v>193</v>
-      </c>
-      <c r="E4" s="44">
-        <v>46054.0</v>
-      </c>
-      <c r="F4" s="42">
+      <c r="D4" s="31" t="s">
+        <v>199</v>
+      </c>
+      <c r="E4" s="32" t="s">
+        <v>127</v>
+      </c>
+      <c r="F4" s="41">
         <v>8.0</v>
       </c>
-      <c r="G4" s="42">
+      <c r="G4" s="36">
         <v>10.0</v>
       </c>
-      <c r="H4" s="42">
+      <c r="H4" s="36">
         <v>10.0</v>
       </c>
-      <c r="I4" s="42">
+      <c r="I4" s="36">
         <v>10.0</v>
       </c>
-      <c r="J4" s="42">
+      <c r="J4" s="36">
         <v>10.0</v>
       </c>
       <c r="K4" s="36">
@@ -12832,81 +12834,80 @@
     <col customWidth="1" min="6" max="9" width="12.0"/>
     <col customWidth="1" min="10" max="10" width="20.0"/>
     <col customWidth="1" min="11" max="11" width="12.0"/>
-    <col customWidth="1" min="12" max="26" width="8.63"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.75" customHeight="1">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="19" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="2" ht="36.0" customHeight="1">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="21" t="s">
+      <c r="B2" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="C2" s="21" t="s">
+      <c r="C2" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="D2" s="21" t="s">
+      <c r="D2" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="E2" s="21" t="s">
+      <c r="E2" s="20" t="s">
         <v>50</v>
       </c>
-      <c r="F2" s="21" t="s">
+      <c r="F2" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="G2" s="21" t="s">
+      <c r="G2" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="H2" s="21" t="s">
+      <c r="H2" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="I2" s="21" t="s">
+      <c r="I2" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="J2" s="21" t="s">
+      <c r="J2" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="K2" s="21" t="s">
+      <c r="K2" s="20" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="22">
+      <c r="A3" s="21">
         <v>103.0</v>
       </c>
-      <c r="B3" s="23">
+      <c r="B3" s="22">
         <v>46221.0</v>
       </c>
-      <c r="C3" s="22" t="s">
-        <v>120</v>
-      </c>
-      <c r="D3" s="47" t="s">
-        <v>194</v>
-      </c>
-      <c r="E3" s="46">
-        <v>46177.0</v>
-      </c>
-      <c r="F3" s="41">
+      <c r="C3" s="21" t="s">
+        <v>122</v>
+      </c>
+      <c r="D3" s="23" t="s">
+        <v>200</v>
+      </c>
+      <c r="E3" s="24" t="s">
+        <v>201</v>
+      </c>
+      <c r="F3" s="28">
         <v>10.0</v>
       </c>
-      <c r="G3" s="41">
+      <c r="G3" s="28">
         <v>10.0</v>
       </c>
-      <c r="H3" s="41">
+      <c r="H3" s="28">
         <v>10.0</v>
       </c>
-      <c r="I3" s="41">
+      <c r="I3" s="28">
         <v>7.0</v>
       </c>
-      <c r="J3" s="41">
+      <c r="J3" s="28">
         <v>7.0</v>
       </c>
-      <c r="K3" s="29">
+      <c r="K3" s="28">
         <f>IF(COUNT(F3:J3)&lt;5,"",ROUND((F3*Quesitos!$B$3+G3*Quesitos!$B$4+H3*Quesitos!$B$5+I3*Quesitos!$B$6+J3*Quesitos!$B$7)/SUM(Quesitos!$B$3:$B$7),2))</f>
         <v>9.1</v>
       </c>
@@ -13950,71 +13951,82 @@
     <col customWidth="1" min="6" max="9" width="12.0"/>
     <col customWidth="1" min="10" max="10" width="20.0"/>
     <col customWidth="1" min="11" max="11" width="12.0"/>
-    <col customWidth="1" min="12" max="26" width="8.63"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.75" customHeight="1">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="19" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="2" ht="36.0" customHeight="1">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="21" t="s">
+      <c r="B2" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="C2" s="21" t="s">
+      <c r="C2" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="D2" s="21" t="s">
+      <c r="D2" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="E2" s="21" t="s">
+      <c r="E2" s="20" t="s">
         <v>50</v>
       </c>
-      <c r="F2" s="21" t="s">
+      <c r="F2" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="G2" s="21" t="s">
+      <c r="G2" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="H2" s="21" t="s">
+      <c r="H2" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="I2" s="21" t="s">
+      <c r="I2" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="J2" s="21" t="s">
+      <c r="J2" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="K2" s="21" t="s">
+      <c r="K2" s="20" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="22">
+      <c r="A3" s="21">
         <v>104.0</v>
       </c>
-      <c r="B3" s="23">
+      <c r="B3" s="22">
         <v>46222.0</v>
       </c>
-      <c r="C3" s="22" t="s">
+      <c r="C3" s="21" t="s">
         <v>52</v>
       </c>
-      <c r="D3" s="47" t="s">
-        <v>195</v>
-      </c>
-      <c r="E3" s="22"/>
-      <c r="F3" s="29"/>
-      <c r="G3" s="29"/>
-      <c r="H3" s="29"/>
-      <c r="I3" s="29"/>
-      <c r="J3" s="29"/>
-      <c r="K3" s="29" t="str">
+      <c r="D3" s="23" t="s">
+        <v>202</v>
+      </c>
+      <c r="E3" s="44" t="s">
+        <v>78</v>
+      </c>
+      <c r="F3" s="43">
+        <v>6.0</v>
+      </c>
+      <c r="G3" s="43">
+        <v>9.0</v>
+      </c>
+      <c r="H3" s="43">
+        <v>2.0</v>
+      </c>
+      <c r="I3" s="43">
+        <v>10.0</v>
+      </c>
+      <c r="J3" s="43">
+        <v>10.0</v>
+      </c>
+      <c r="K3" s="28">
         <f>IF(COUNT(F3:J3)&lt;5,"",ROUND((F3*Quesitos!$B$3+G3*Quesitos!$B$4+H3*Quesitos!$B$5+I3*Quesitos!$B$6+J3*Quesitos!$B$7)/SUM(Quesitos!$B$3:$B$7),2))</f>
-        <v/>
+        <v>7.15</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>

--- a/Notas_da_Copa_2026.xlsx
+++ b/Notas_da_Copa_2026.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="204">
   <si>
     <t>Controle de notas — Copa do Mundo 2026</t>
   </si>
@@ -633,6 +633,9 @@
   </si>
   <si>
     <t>Espanha x Argentina</t>
+  </si>
+  <si>
+    <t>2-3</t>
   </si>
 </sst>
 </file>
@@ -9251,7 +9254,7 @@
         <v>188</v>
       </c>
       <c r="E6" s="32" t="s">
-        <v>125</v>
+        <v>203</v>
       </c>
       <c r="F6" s="36">
         <v>7.0</v>

--- a/Notas_da_Copa_2026.xlsx
+++ b/Notas_da_Copa_2026.xlsx
@@ -4658,7 +4658,7 @@
         <v>97</v>
       </c>
       <c r="E25" s="24" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="F25" s="28">
         <v>2.0</v>
